--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -2336,11 +2336,11 @@
         <v>SOL</v>
       </c>
       <c r="B3" s="15">
-        <v>106.09</v>
+        <v>106.04</v>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:01:38.255Z</t>
+          <t>2026-09-18T09:14:29.228Z</t>
         </is>
       </c>
       <c r="D3" s="13" t="str">
@@ -2352,11 +2352,11 @@
         <v>BNB</v>
       </c>
       <c r="B4" s="15">
-        <v>753.88</v>
+        <v>753.48</v>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:01:38.255Z</t>
+          <t>2026-09-18T09:14:29.228Z</t>
         </is>
       </c>
       <c r="D4" s="13" t="str">
@@ -2368,11 +2368,11 @@
         <v>HYPE</v>
       </c>
       <c r="B5" s="15">
-        <v>88.57</v>
+        <v>88.49</v>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:01:38.255Z</t>
+          <t>2026-09-18T09:14:29.228Z</t>
         </is>
       </c>
       <c r="D5" s="13" t="str">
@@ -2384,11 +2384,11 @@
         <v>ASTER</v>
       </c>
       <c r="B6" s="15">
-        <v>0.754061</v>
+        <v>0.754569</v>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:01:38.255Z</t>
+          <t>2026-09-18T09:14:29.228Z</t>
         </is>
       </c>
       <c r="D6" s="13" t="str">
@@ -2400,11 +2400,11 @@
         <v>ETH</v>
       </c>
       <c r="B7" s="92">
-        <v>2500.87</v>
+        <v>2506.4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-18T09:01:38.255Z</t>
+          <t>2026-09-18T09:14:29.228Z</t>
         </is>
       </c>
       <c r="D7" t="str">
@@ -2446,14 +2446,14 @@
         <v>USDT / USD</v>
       </c>
       <c r="B12" s="552">
-        <v>0.999164</v>
+        <v>0.999177</v>
       </c>
       <c r="C12" t="str">
         <v>汇率快照</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-18T09:01:38.255Z</t>
+          <t>2026-09-18T09:14:29.228Z</t>
         </is>
       </c>
     </row>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -2336,11 +2336,11 @@
         <v>SOL</v>
       </c>
       <c r="B3" s="15">
-        <v>106.04</v>
+        <v>106</v>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:14:29.228Z</t>
+          <t>2026-09-18T09:31:01.466Z</t>
         </is>
       </c>
       <c r="D3" s="13" t="str">
@@ -2352,11 +2352,11 @@
         <v>BNB</v>
       </c>
       <c r="B4" s="15">
-        <v>753.48</v>
+        <v>752.11</v>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:14:29.228Z</t>
+          <t>2026-09-18T09:31:01.466Z</t>
         </is>
       </c>
       <c r="D4" s="13" t="str">
@@ -2368,11 +2368,11 @@
         <v>HYPE</v>
       </c>
       <c r="B5" s="15">
-        <v>88.49</v>
+        <v>88.61</v>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:14:29.228Z</t>
+          <t>2026-09-18T09:31:01.466Z</t>
         </is>
       </c>
       <c r="D5" s="13" t="str">
@@ -2384,11 +2384,11 @@
         <v>ASTER</v>
       </c>
       <c r="B6" s="15">
-        <v>0.754569</v>
+        <v>0.753084</v>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:14:29.228Z</t>
+          <t>2026-09-18T09:31:01.466Z</t>
         </is>
       </c>
       <c r="D6" s="13" t="str">
@@ -2400,11 +2400,11 @@
         <v>ETH</v>
       </c>
       <c r="B7" s="92">
-        <v>2506.4</v>
+        <v>2506.62</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-18T09:14:29.228Z</t>
+          <t>2026-09-18T09:31:01.466Z</t>
         </is>
       </c>
       <c r="D7" t="str">
@@ -2446,14 +2446,14 @@
         <v>USDT / USD</v>
       </c>
       <c r="B12" s="552">
-        <v>0.999177</v>
+        <v>0.999197</v>
       </c>
       <c r="C12" t="str">
         <v>汇率快照</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-18T09:14:29.228Z</t>
+          <t>2026-09-18T09:31:01.466Z</t>
         </is>
       </c>
     </row>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -2336,11 +2336,11 @@
         <v>SOL</v>
       </c>
       <c r="B3" s="15">
-        <v>106</v>
+        <v>105.92</v>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:31:01.466Z</t>
+          <t>2026-09-18T09:34:59.631Z</t>
         </is>
       </c>
       <c r="D3" s="13" t="str">
@@ -2352,11 +2352,11 @@
         <v>BNB</v>
       </c>
       <c r="B4" s="15">
-        <v>752.11</v>
+        <v>751.26</v>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:31:01.466Z</t>
+          <t>2026-09-18T09:34:59.631Z</t>
         </is>
       </c>
       <c r="D4" s="13" t="str">
@@ -2368,11 +2368,11 @@
         <v>HYPE</v>
       </c>
       <c r="B5" s="15">
-        <v>88.61</v>
+        <v>88.68</v>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:31:01.466Z</t>
+          <t>2026-09-18T09:34:59.631Z</t>
         </is>
       </c>
       <c r="D5" s="13" t="str">
@@ -2384,11 +2384,11 @@
         <v>ASTER</v>
       </c>
       <c r="B6" s="15">
-        <v>0.753084</v>
+        <v>0.752214</v>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:31:01.466Z</t>
+          <t>2026-09-18T09:34:59.631Z</t>
         </is>
       </c>
       <c r="D6" s="13" t="str">
@@ -2400,11 +2400,11 @@
         <v>ETH</v>
       </c>
       <c r="B7" s="92">
-        <v>2506.62</v>
+        <v>2504.07</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-18T09:31:01.466Z</t>
+          <t>2026-09-18T09:34:59.631Z</t>
         </is>
       </c>
       <c r="D7" t="str">
@@ -2446,14 +2446,14 @@
         <v>USDT / USD</v>
       </c>
       <c r="B12" s="552">
-        <v>0.999197</v>
+        <v>0.999193</v>
       </c>
       <c r="C12" t="str">
         <v>汇率快照</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-18T09:31:01.466Z</t>
+          <t>2026-09-18T09:34:59.631Z</t>
         </is>
       </c>
     </row>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -2336,11 +2336,11 @@
         <v>SOL</v>
       </c>
       <c r="B3" s="15">
-        <v>105.92</v>
+        <v>105.89</v>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:34:59.631Z</t>
+          <t>2026-09-18T09:36:46.399Z</t>
         </is>
       </c>
       <c r="D3" s="13" t="str">
@@ -2352,11 +2352,11 @@
         <v>BNB</v>
       </c>
       <c r="B4" s="15">
-        <v>751.26</v>
+        <v>751.1</v>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:34:59.631Z</t>
+          <t>2026-09-18T09:36:46.399Z</t>
         </is>
       </c>
       <c r="D4" s="13" t="str">
@@ -2368,11 +2368,11 @@
         <v>HYPE</v>
       </c>
       <c r="B5" s="15">
-        <v>88.68</v>
+        <v>88.73</v>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:34:59.631Z</t>
+          <t>2026-09-18T09:36:46.399Z</t>
         </is>
       </c>
       <c r="D5" s="13" t="str">
@@ -2384,11 +2384,11 @@
         <v>ASTER</v>
       </c>
       <c r="B6" s="15">
-        <v>0.752214</v>
+        <v>0.7521</v>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18T09:34:59.631Z</t>
+          <t>2026-09-18T09:36:46.399Z</t>
         </is>
       </c>
       <c r="D6" s="13" t="str">
@@ -2400,11 +2400,11 @@
         <v>ETH</v>
       </c>
       <c r="B7" s="92">
-        <v>2504.07</v>
+        <v>2503.31</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-18T09:34:59.631Z</t>
+          <t>2026-09-18T09:36:46.399Z</t>
         </is>
       </c>
       <c r="D7" t="str">
@@ -2446,14 +2446,14 @@
         <v>USDT / USD</v>
       </c>
       <c r="B12" s="552">
-        <v>0.999193</v>
+        <v>0.99917</v>
       </c>
       <c r="C12" t="str">
         <v>汇率快照</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-18T09:34:59.631Z</t>
+          <t>2026-09-18T09:36:46.399Z</t>
         </is>
       </c>
     </row>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4530,7 +4530,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.99917</v>
+        <v>0.999175</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4571,7 +4571,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46283.40053702547</v>
+        <v>46283.42145649306</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4924,13 +4924,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>105.97796170821782</v>
+        <v>106.50786899191833</v>
       </c>
       <c r="I14" s="20">
-        <v>105.97796170821782</v>
+        <v>106.50786899191833</v>
       </c>
       <c r="J14" s="23">
-        <v>46283.40053702547</v>
+        <v>46283.42145649306</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5031,13 +5031,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.000830689472262</v>
+        <v>1.0008256811869791</v>
       </c>
       <c r="I15" s="21">
-        <v>105.97796170821782</v>
+        <v>106.50786899191833</v>
       </c>
       <c r="J15" s="24">
-        <v>46283.40053702547</v>
+        <v>46283.42145649306</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5138,13 +5138,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.000830689472262</v>
+        <v>1.0008256811869791</v>
       </c>
       <c r="I16" s="21">
-        <v>751.723930862616</v>
+        <v>751.1396902444516</v>
       </c>
       <c r="J16" s="24">
-        <v>46283.40053702547</v>
+        <v>46283.42145649306</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5245,13 +5245,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>751.723930862616</v>
+        <v>751.1396902444516</v>
       </c>
       <c r="I17" s="21">
-        <v>751.723930862616</v>
+        <v>751.1396902444516</v>
       </c>
       <c r="J17" s="24">
-        <v>46283.40053702547</v>
+        <v>46283.42145649306</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5352,13 +5352,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7527247615520882</v>
+        <v>0.7559316436059749</v>
       </c>
       <c r="I18" s="21">
-        <v>751.723930862616</v>
+        <v>751.1396902444516</v>
       </c>
       <c r="J18" s="24">
-        <v>46283.40053702547</v>
+        <v>46283.42145649306</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5459,13 +5459,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>88.8037070768738</v>
+        <v>89.20359296419545</v>
       </c>
       <c r="I19" s="21">
-        <v>88.8037070768738</v>
+        <v>89.20359296419545</v>
       </c>
       <c r="J19" s="24">
-        <v>46283.40053702547</v>
+        <v>46283.42145649306</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5566,13 +5566,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>751.723930862616</v>
+        <v>751.1396902444516</v>
       </c>
       <c r="I20" s="21">
-        <v>751.723930862616</v>
+        <v>751.1396902444516</v>
       </c>
       <c r="J20" s="24">
-        <v>46283.40053702547</v>
+        <v>46283.42145649306</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5673,13 +5673,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.000830689472262</v>
+        <v>1.0008256811869791</v>
       </c>
       <c r="I21" s="21">
-        <v>751.723930862616</v>
+        <v>751.1396902444516</v>
       </c>
       <c r="J21" s="24">
-        <v>46283.40053702547</v>
+        <v>46283.42145649306</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5780,13 +5780,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2505.389473262808</v>
+        <v>2511.6521129932194</v>
       </c>
       <c r="I22" s="22">
-        <v>2505.389473262808</v>
+        <v>2511.6521129932194</v>
       </c>
       <c r="J22" s="25">
-        <v>46283.40053702547</v>
+        <v>46283.42145649306</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4530,7 +4530,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999175</v>
+        <v>0.999657</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4571,7 +4571,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46283.42145649306</v>
+        <v>46284.256953414355</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4924,13 +4924,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>106.50786899191833</v>
+        <v>111.958401731794</v>
       </c>
       <c r="I14" s="20">
-        <v>106.50786899191833</v>
+        <v>111.958401731794</v>
       </c>
       <c r="J14" s="23">
-        <v>46283.42145649306</v>
+        <v>46284.256953414355</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5031,13 +5031,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0008256811869791</v>
+        <v>1.0003431176893673</v>
       </c>
       <c r="I15" s="21">
-        <v>106.50786899191833</v>
+        <v>111.958401731794</v>
       </c>
       <c r="J15" s="24">
-        <v>46283.42145649306</v>
+        <v>46284.256953414355</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5138,13 +5138,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0008256811869791</v>
+        <v>1.0003431176893673</v>
       </c>
       <c r="I16" s="21">
-        <v>751.1396902444516</v>
+        <v>763.5118845764097</v>
       </c>
       <c r="J16" s="24">
-        <v>46283.42145649306</v>
+        <v>46284.256953414355</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5245,13 +5245,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>751.1396902444516</v>
+        <v>763.5118845764097</v>
       </c>
       <c r="I17" s="21">
-        <v>751.1396902444516</v>
+        <v>763.5118845764097</v>
       </c>
       <c r="J17" s="24">
-        <v>46283.42145649306</v>
+        <v>46284.256953414355</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5352,13 +5352,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7559316436059749</v>
+        <v>0.7704702713030569</v>
       </c>
       <c r="I18" s="21">
-        <v>751.1396902444516</v>
+        <v>763.5118845764097</v>
       </c>
       <c r="J18" s="24">
-        <v>46283.42145649306</v>
+        <v>46284.256953414355</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5459,13 +5459,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>89.20359296419545</v>
+        <v>92.22163201978279</v>
       </c>
       <c r="I19" s="21">
-        <v>89.20359296419545</v>
+        <v>92.22163201978279</v>
       </c>
       <c r="J19" s="24">
-        <v>46283.42145649306</v>
+        <v>46284.256953414355</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5566,13 +5566,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>751.1396902444516</v>
+        <v>763.5118845764097</v>
       </c>
       <c r="I20" s="21">
-        <v>751.1396902444516</v>
+        <v>763.5118845764097</v>
       </c>
       <c r="J20" s="24">
-        <v>46283.42145649306</v>
+        <v>46284.256953414355</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5673,13 +5673,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0008256811869791</v>
+        <v>1.0003431176893673</v>
       </c>
       <c r="I21" s="21">
-        <v>751.1396902444516</v>
+        <v>763.5118845764097</v>
       </c>
       <c r="J21" s="24">
-        <v>46283.42145649306</v>
+        <v>46284.256953414355</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5780,13 +5780,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2511.6521129932194</v>
+        <v>2629.1017819111953</v>
       </c>
       <c r="I22" s="22">
-        <v>2511.6521129932194</v>
+        <v>2629.1017819111953</v>
       </c>
       <c r="J22" s="25">
-        <v>46283.42145649306</v>
+        <v>46284.256953414355</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4530,7 +4530,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999657</v>
+        <v>0.999604</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4571,7 +4571,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46284.256953414355</v>
+        <v>46285.27349457176</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4924,13 +4924,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>111.958401731794</v>
+        <v>108.53297905970763</v>
       </c>
       <c r="I14" s="20">
-        <v>111.958401731794</v>
+        <v>108.53297905970763</v>
       </c>
       <c r="J14" s="23">
-        <v>46284.256953414355</v>
+        <v>46285.27349457176</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5031,13 +5031,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0003431176893673</v>
+        <v>1.0003961568781237</v>
       </c>
       <c r="I15" s="21">
-        <v>111.958401731794</v>
+        <v>108.53297905970763</v>
       </c>
       <c r="J15" s="24">
-        <v>46284.256953414355</v>
+        <v>46285.27349457176</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5138,13 +5138,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0003431176893673</v>
+        <v>1.0003961568781237</v>
       </c>
       <c r="I16" s="21">
-        <v>763.5118845764097</v>
+        <v>752.7981080507881</v>
       </c>
       <c r="J16" s="24">
-        <v>46284.256953414355</v>
+        <v>46285.27349457176</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5245,13 +5245,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>763.5118845764097</v>
+        <v>752.7981080507881</v>
       </c>
       <c r="I17" s="21">
-        <v>763.5118845764097</v>
+        <v>752.7981080507881</v>
       </c>
       <c r="J17" s="24">
-        <v>46284.256953414355</v>
+        <v>46285.27349457176</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5352,13 +5352,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7704702713030569</v>
+        <v>0.7357363515952317</v>
       </c>
       <c r="I18" s="21">
-        <v>763.5118845764097</v>
+        <v>752.7981080507881</v>
       </c>
       <c r="J18" s="24">
-        <v>46284.256953414355</v>
+        <v>46285.27349457176</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5459,13 +5459,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>92.22163201978279</v>
+        <v>91.08607008375316</v>
       </c>
       <c r="I19" s="21">
-        <v>92.22163201978279</v>
+        <v>91.08607008375316</v>
       </c>
       <c r="J19" s="24">
-        <v>46284.256953414355</v>
+        <v>46285.27349457176</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5566,13 +5566,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>763.5118845764097</v>
+        <v>752.7981080507881</v>
       </c>
       <c r="I20" s="21">
-        <v>763.5118845764097</v>
+        <v>752.7981080507881</v>
       </c>
       <c r="J20" s="24">
-        <v>46284.256953414355</v>
+        <v>46285.27349457176</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5673,13 +5673,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0003431176893673</v>
+        <v>1.0003961568781237</v>
       </c>
       <c r="I21" s="21">
-        <v>763.5118845764097</v>
+        <v>752.7981080507881</v>
       </c>
       <c r="J21" s="24">
-        <v>46284.256953414355</v>
+        <v>46285.27349457176</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5780,13 +5780,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2629.1017819111953</v>
+        <v>2580.0817123580937</v>
       </c>
       <c r="I22" s="22">
-        <v>2629.1017819111953</v>
+        <v>2580.0817123580937</v>
       </c>
       <c r="J22" s="25">
-        <v>46284.256953414355</v>
+        <v>46285.27349457176</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="Rd38f9e7e06ea46ad"/>
-    <sheet name="Quote参数" sheetId="2" r:id="Ra7375a2e5dfc433b"/>
+    <sheet name="控筹模型" sheetId="1" r:id="Ra4a3221c8ea9478b"/>
+    <sheet name="Quote参数" sheetId="2" r:id="Rf51891fb9c854582"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -839,7 +839,7 @@
         <v>买入税率（Flap）</v>
       </c>
       <c r="J7" s="55">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,25,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,25,FALSE)</f>
       </c>
       <c r="K7" s="49"/>
       <c r="L7" s="49"/>
@@ -863,7 +863,7 @@
         <v>卖出税率（Flap）</v>
       </c>
       <c r="J8" s="55">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,26,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,26,FALSE)</f>
       </c>
       <c r="K8" s="49"/>
       <c r="L8" s="49"/>
@@ -885,7 +885,7 @@
         <v>Creator Tax（Pons）</v>
       </c>
       <c r="J9" s="55">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,27,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,27,FALSE)</f>
       </c>
       <c r="K9" s="49"/>
       <c r="L9" s="49"/>
@@ -924,7 +924,7 @@
         <v>单地址 Gas</v>
       </c>
       <c r="G11" s="54">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,33,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,33,FALSE)</f>
       </c>
       <c r="H11" s="49"/>
       <c r="I11" s="49"/>
@@ -951,7 +951,7 @@
         <v>洗筹基础费率</v>
       </c>
       <c r="J12" s="55">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,20,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,20,FALSE)</f>
       </c>
       <c r="K12" s="49"/>
       <c r="L12" s="49"/>
@@ -1028,7 +1028,7 @@
         <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
       </c>
       <c r="E18" s="48">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
       </c>
       <c r="F18" s="3" t="str">
         <v>原生币 Gas 储备</v>
@@ -1037,7 +1037,7 @@
         <f>D53*MAX(0,G11)</f>
       </c>
       <c r="H18" s="48">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,4,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,4,FALSE)</f>
       </c>
       <c r="I18" s="3" t="str">
         <v>总折算 / USDT</v>
@@ -1110,7 +1110,7 @@
         <f>IF($D$51&lt;&gt;"可达","",$J$41+IF($G$40="pons",$G$50/$J$51-$G$49,IF($G$40="four-stock",($G$50/$J$50-$G$49)/(1-$G$42),($G$50/$J$50-$G$49)*(1+$G$42))))</f>
       </c>
       <c r="E22" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -1130,7 +1130,7 @@
         <f>IF($D$51="可达",$J$41*MAX(0,$G$7-1),"")</f>
       </c>
       <c r="E23" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -1152,7 +1152,7 @@
         <f>IF($D$51="可达",$J$52*$D$29,"")</f>
       </c>
       <c r="E24" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -1174,7 +1174,7 @@
         <f>IF($D$51="可达",$G$12,"")</f>
       </c>
       <c r="E25" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -1193,10 +1193,10 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="65">
-        <f>IF($D$51&lt;&gt;"可达","",IF($G$40="pons",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*(1+$G$42)),"")))</f>
+        <f>IF($D$51&lt;&gt;"可达","",IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,34,FALSE)="quote",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*IF($G$40="pons",1,IF($G$40="four-stock",1/(1-$G$42),1+$G$42))),"")))</f>
       </c>
       <c r="E26" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="41" t="str">
-        <v>目标持仓全部洗一轮，以卖出所得买回。补回为小单固定价 + 现有外盘曲线差额的保守预留，损耗仍按目标加缓冲 FDV；非逐笔模拟。Pons 按原批准口径持仓不降、补回为 0。</v>
+        <v>外盘手续费只在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，损耗仍按目标加缓冲 FDV；非逐笔模拟。</v>
       </c>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
@@ -1362,10 +1362,10 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="65">
-        <f>IF($G$40="four-stock",E126,VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,23,FALSE))</f>
+        <f>IF($G$40="four-stock",E126,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,23,FALSE))</f>
       </c>
       <c r="H37" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
@@ -1406,7 +1406,7 @@
         <v>模型类型</v>
       </c>
       <c r="G40" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,10,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,10,FALSE)</f>
       </c>
       <c r="H40" s="49"/>
       <c r="I40" s="49"/>
@@ -1422,7 +1422,7 @@
         <v>内盘基础费</v>
       </c>
       <c r="G41" s="58">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,19,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,19,FALSE)</f>
       </c>
       <c r="H41" s="49"/>
       <c r="I41" s="49" t="str">
@@ -1442,7 +1442,7 @@
         <v>外盘基础费</v>
       </c>
       <c r="G42" s="58">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,20,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,20,FALSE)</f>
       </c>
       <c r="H42" s="49"/>
       <c r="I42" s="49"/>
@@ -1458,14 +1458,14 @@
         <v>毕业控筹率</v>
       </c>
       <c r="G43" s="58">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,15,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,15,FALSE)</f>
       </c>
       <c r="H43" s="49"/>
       <c r="I43" s="49" t="str">
         <v>模型键</v>
       </c>
       <c r="J43" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,2,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,2,FALSE)</f>
       </c>
       <c r="K43" s="49"/>
       <c r="L43" s="49"/>
@@ -1478,14 +1478,14 @@
         <v>内盘初始 TOKEN</v>
       </c>
       <c r="G44" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,12,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,12,FALSE)</f>
       </c>
       <c r="H44" s="49"/>
       <c r="I44" s="49" t="str">
         <v>原生币价格 / USDT</v>
       </c>
       <c r="J44" s="49">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,3,FALSE)=VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,4,FALSE),$D$55,VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,7,FALSE))</f>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)=VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,4,FALSE),$D$55,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,7,FALSE))</f>
       </c>
       <c r="K44" s="49"/>
       <c r="L44" s="49"/>
@@ -1495,21 +1495,21 @@
         <v>总供应量</v>
       </c>
       <c r="D45" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,11,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,11,FALSE)</f>
       </c>
       <c r="E45" s="49"/>
       <c r="F45" s="49" t="str">
         <v>内盘初始 Quote</v>
       </c>
       <c r="G45" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,13,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,13,FALSE)</f>
       </c>
       <c r="H45" s="49"/>
       <c r="I45" s="49" t="str">
         <v>税率上限</v>
       </c>
       <c r="J45" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,32,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,32,FALSE)</f>
       </c>
       <c r="K45" s="49"/>
       <c r="L45" s="49"/>
@@ -1522,7 +1522,7 @@
         <v>内盘 K</v>
       </c>
       <c r="G46" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,14,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,14,FALSE)</f>
       </c>
       <c r="H46" s="49"/>
       <c r="I46" s="49" t="str">
@@ -1558,7 +1558,7 @@
         <v>外盘初始 TOKEN</v>
       </c>
       <c r="G48" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,16,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,16,FALSE)</f>
       </c>
       <c r="H48" s="49"/>
       <c r="I48" s="49" t="str">
@@ -1578,7 +1578,7 @@
         <v>外盘初始 Quote</v>
       </c>
       <c r="G49" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,17,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,17,FALSE)</f>
       </c>
       <c r="H49" s="49"/>
       <c r="I49" s="49"/>
@@ -1594,7 +1594,7 @@
         <v>外盘 K</v>
       </c>
       <c r="G50" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,18,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,18,FALSE)</f>
       </c>
       <c r="H50" s="49"/>
       <c r="I50" s="49" t="str">
@@ -1618,7 +1618,7 @@
         <v>永久锁仓 TOKEN</v>
       </c>
       <c r="G51" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,22,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,22,FALSE)</f>
       </c>
       <c r="H51" s="49"/>
       <c r="I51" s="49" t="str">
@@ -1642,7 +1642,7 @@
         <v>一套内盘原值</v>
       </c>
       <c r="G52" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,21,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,21,FALSE)</f>
       </c>
       <c r="H52" s="49"/>
       <c r="I52" s="49" t="str">
@@ -1666,7 +1666,7 @@
         <v>内盘募集 Quote</v>
       </c>
       <c r="G53" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,24,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,24,FALSE)</f>
       </c>
       <c r="H53" s="49"/>
       <c r="I53" s="49"/>
@@ -1693,7 +1693,7 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="58">
-        <f>IF($G$40="pons",1,(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))^2)</f>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,34,FALSE)="quote",1,IF($G$40="pons",MAX(0,1-MAX(0,$J$12)-$J$48),(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))))</f>
       </c>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -1703,21 +1703,21 @@
         <v>有效价格 / USDT</v>
       </c>
       <c r="D55" s="60">
-        <f>IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,IF(AND(ISNUMBER(VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,6,FALSE)),VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,6,FALSE)&gt;0),VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,6,FALSE),""))</f>
+        <f>IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,IF(AND(ISNUMBER(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,6,FALSE)),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,6,FALSE)&gt;0),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,6,FALSE),""))</f>
       </c>
       <c r="E55" s="49"/>
       <c r="F55" s="49" t="str">
         <v>价格来源</v>
       </c>
       <c r="G55" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,9,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,9,FALSE)</f>
       </c>
       <c r="H55" s="49"/>
       <c r="I55" s="49" t="str">
         <v>目标外盘 TOKEN</v>
       </c>
       <c r="J55" s="49">
-        <f>IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$8)-$G$51,IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8))))</f>
+        <f>IF($G$40="pons",$G$48-MAX(0,($D$8-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$8)-$G$51,IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8)))))</f>
       </c>
       <c r="K55" s="49"/>
       <c r="L55" s="49"/>
@@ -1727,7 +1727,7 @@
         <v>价格时间 / UTC</v>
       </c>
       <c r="D56" s="61">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$22,8,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,8,FALSE)</f>
       </c>
       <c r="E56" s="49"/>
       <c r="F56" s="49" t="str">
@@ -1741,7 +1741,7 @@
         <v>洗后外盘 TOKEN</v>
       </c>
       <c r="J56" s="49">
-        <f>IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27))))</f>
+        <f>IF($G$40="pons",$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27)))))</f>
       </c>
       <c r="K56" s="49"/>
       <c r="L56" s="49"/>
@@ -4332,6 +4332,9 @@
     <col min="33" max="33" width="44" hidden="0" customWidth="1"/>
     <col min="34" max="34" width="20" hidden="0" customWidth="1"/>
     <col min="35" max="35" width="20" hidden="0" customWidth="1"/>
+    <col min="36" max="36" width="20" hidden="0" customWidth="1"/>
+    <col min="37" max="37" width="44" hidden="0" customWidth="1"/>
+    <col min="38" max="38" width="44" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4370,6 +4373,9 @@
       <c r="AG1" s="5"/>
       <c r="AH1" s="5"/>
       <c r="AI1" s="5"/>
+      <c r="AJ1" s="5"/>
+      <c r="AK1" s="5"/>
+      <c r="AL1" s="5"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="5"/>
@@ -4409,6 +4415,9 @@
       <c r="AG2" s="7"/>
       <c r="AH2" s="7"/>
       <c r="AI2" s="7"/>
+      <c r="AJ2" s="7"/>
+      <c r="AK2" s="7"/>
+      <c r="AL2" s="7"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="5"/>
@@ -4448,6 +4457,9 @@
       <c r="AG3" s="5"/>
       <c r="AH3" s="5"/>
       <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="5"/>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="5"/>
@@ -4485,6 +4497,9 @@
       <c r="AG4" s="5"/>
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="5"/>
@@ -4522,6 +4537,9 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5"/>
       <c r="AI5" s="5"/>
+      <c r="AJ5" s="5"/>
+      <c r="AK5" s="5"/>
+      <c r="AL5" s="5"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="5"/>
@@ -4563,6 +4581,9 @@
       <c r="AG6" s="5"/>
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
+      <c r="AJ6" s="5"/>
+      <c r="AK6" s="5"/>
+      <c r="AL6" s="5"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="5"/>
@@ -4604,6 +4625,9 @@
       <c r="AG7" s="5"/>
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
+      <c r="AJ7" s="5"/>
+      <c r="AK7" s="5"/>
+      <c r="AL7" s="5"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="5"/>
@@ -4647,6 +4671,9 @@
       <c r="AG8" s="5"/>
       <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
+      <c r="AJ8" s="5"/>
+      <c r="AK8" s="5"/>
+      <c r="AL8" s="5"/>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="5"/>
@@ -4684,6 +4711,9 @@
       <c r="AG9" s="5"/>
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
+      <c r="AJ9" s="5"/>
+      <c r="AK9" s="5"/>
+      <c r="AL9" s="5"/>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="5"/>
@@ -4725,6 +4755,9 @@
       <c r="AG10" s="5"/>
       <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
+      <c r="AJ10" s="5"/>
+      <c r="AK10" s="5"/>
+      <c r="AL10" s="5"/>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="5"/>
@@ -4733,7 +4766,7 @@
         <v>洗筹与补回口径</v>
       </c>
       <c r="D11" s="12" t="str">
-        <v>损耗按目标加缓冲的 FDV × 双边费率。非 Pons 的补回按目标持仓洗一轮、小单固定价及现有外盘曲线差额估算；Pons 按原批准的 Quote 预算承担手续费，补回为 0。非逐笔模拟。</v>
+        <v>损耗按目标加缓冲的 FDV × 双边费率。外盘手续费仅在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，非逐笔模拟。</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -4766,6 +4799,9 @@
       <c r="AG11" s="5"/>
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
+      <c r="AJ11" s="5"/>
+      <c r="AK11" s="5"/>
+      <c r="AL11" s="5"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="5"/>
@@ -4803,6 +4839,9 @@
       <c r="AG12" s="5"/>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
+      <c r="AJ12" s="5"/>
+      <c r="AK12" s="5"/>
+      <c r="AL12" s="5"/>
     </row>
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="5"/>
@@ -4906,6 +4945,15 @@
       <c r="AI13" s="16" t="str">
         <v>单地址 Gas</v>
       </c>
+      <c r="AJ13" s="16" t="str">
+        <v>外盘扣费资产</v>
+      </c>
+      <c r="AK13" s="16" t="str">
+        <v>外盘扣费机制</v>
+      </c>
+      <c r="AL13" s="16" t="str">
+        <v>扣费机制来源</v>
+      </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="5"/>
@@ -5013,6 +5061,15 @@
       <c r="AI14" s="17" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ14" s="26" t="str">
+        <v>quote</v>
+      </c>
+      <c r="AK14" s="35" t="str">
+        <v>买卖两侧均以 Quote 收取，不直接扣除 Meme TOKEN</v>
+      </c>
+      <c r="AL14" s="35" t="str">
+        <v>https://github.com/pump-fun/pump-public-docs/blob/main/docs/instructions/BUY.md</v>
+      </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="5"/>
@@ -5120,6 +5177,15 @@
       <c r="AI15" s="18" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ15" s="27" t="str">
+        <v>input</v>
+      </c>
+      <c r="AK15" s="36" t="str">
+        <v>Raydium CPMM 从每笔 Swap 的输入币扣费；卖出侧输入币为 Meme TOKEN</v>
+      </c>
+      <c r="AL15" s="36" t="str">
+        <v>https://docs.raydium.io/raydium/build/developers-zh/cao-zuo-fang-fa/ru-he-she-zhi-cpmm-fei-yong</v>
+      </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="5"/>
@@ -5227,6 +5293,15 @@
       <c r="AI16" s="18" t="n">
         <v>0.01</v>
       </c>
+      <c r="AJ16" s="27" t="str">
+        <v>input</v>
+      </c>
+      <c r="AK16" s="36" t="str">
+        <v>PancakeSwap 从每笔 Swap 的输入币扣费；卖出侧输入币为 Meme TOKEN</v>
+      </c>
+      <c r="AL16" s="36" t="str">
+        <v>https://docs.pancakeswap.finance/trade/pancakeswap-exchange/trade</v>
+      </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="5"/>
@@ -5334,6 +5409,15 @@
       <c r="AI17" s="18" t="n">
         <v>0.01</v>
       </c>
+      <c r="AJ17" s="27" t="str">
+        <v>input</v>
+      </c>
+      <c r="AK17" s="36" t="str">
+        <v>PancakeSwap 从每笔 Swap 的输入币扣费；卖出侧输入币为 Meme TOKEN</v>
+      </c>
+      <c r="AL17" s="36" t="str">
+        <v>https://docs.pancakeswap.finance/trade/pancakeswap-exchange/trade</v>
+      </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="5"/>
@@ -5441,6 +5525,15 @@
       <c r="AI18" s="18" t="n">
         <v>0.01</v>
       </c>
+      <c r="AJ18" s="27" t="str">
+        <v>input</v>
+      </c>
+      <c r="AK18" s="36" t="str">
+        <v>PancakeSwap 从每笔 Swap 的输入币扣费；卖出侧输入币为 Meme TOKEN</v>
+      </c>
+      <c r="AL18" s="36" t="str">
+        <v>https://docs.pancakeswap.finance/trade/pancakeswap-exchange/trade</v>
+      </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="5"/>
@@ -5548,6 +5641,15 @@
       <c r="AI19" s="18" t="n">
         <v>0.1</v>
       </c>
+      <c r="AJ19" s="27" t="str">
+        <v>input</v>
+      </c>
+      <c r="AK19" s="36" t="str">
+        <v>HyperSwap V2 从每笔 Swap 的输入币扣费；卖出侧输入币为 Meme TOKEN</v>
+      </c>
+      <c r="AL19" s="36" t="str">
+        <v>https://docs.hyperswap.pro/technical-protocol/protocol-overview/how</v>
+      </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="5"/>
@@ -5655,6 +5757,15 @@
       <c r="AI20" s="18" t="n">
         <v>0.01</v>
       </c>
+      <c r="AJ20" s="27" t="str">
+        <v>input</v>
+      </c>
+      <c r="AK20" s="36" t="str">
+        <v>PancakeSwap LP 费从输入币扣取；外盘买税扣输出 TOKEN，卖税扣输入 TOKEN</v>
+      </c>
+      <c r="AL20" s="36" t="str">
+        <v>https://docs.pancakeswap.finance/trade/pancakeswap-exchange/trade</v>
+      </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="5"/>
@@ -5762,6 +5873,15 @@
       <c r="AI21" s="18" t="n">
         <v>0.01</v>
       </c>
+      <c r="AJ21" s="27" t="str">
+        <v>input</v>
+      </c>
+      <c r="AK21" s="36" t="str">
+        <v>PancakeSwap LP 费从输入币扣取；外盘买税扣输出 TOKEN，卖税扣输入 TOKEN</v>
+      </c>
+      <c r="AL21" s="36" t="str">
+        <v>https://docs.pancakeswap.finance/trade/pancakeswap-exchange/trade</v>
+      </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="5"/>
@@ -5868,6 +5988,15 @@
       </c>
       <c r="AI22" s="19" t="n">
         <v>0.005</v>
+      </c>
+      <c r="AJ22" s="28" t="str">
+        <v>output</v>
+      </c>
+      <c r="AK22" s="37" t="str">
+        <v>Pons V4 Hook 从输出币扣费；买入侧输出币为 Meme TOKEN，卖出侧输出币为 Quote</v>
+      </c>
+      <c r="AL22" s="37" t="str">
+        <v>https://docs.ponsfamily.com/v2</v>
       </c>
     </row>
   </sheetData>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="Ra4a3221c8ea9478b"/>
-    <sheet name="Quote参数" sheetId="2" r:id="Rf51891fb9c854582"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R1423d5dfc8cd496e"/>
+    <sheet name="Quote参数" sheetId="2" r:id="Re3e8b4bf065b459b"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -5990,10 +5990,10 @@
         <v>0.005</v>
       </c>
       <c r="AJ22" s="28" t="str">
-        <v>output</v>
+        <v>quote</v>
       </c>
       <c r="AK22" s="37" t="str">
-        <v>Pons V4 Hook 从输出币扣费；买入侧输出币为 Meme TOKEN，卖出侧输出币为 Quote</v>
+        <v>Pons V2 手续费始终按 Quote leg 计收；Hook 暂存的 Meme 费用会在池内转换回 Quote</v>
       </c>
       <c r="AL22" s="37" t="str">
         <v>https://docs.ponsfamily.com/v2</v>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R1423d5dfc8cd496e"/>
-    <sheet name="Quote参数" sheetId="2" r:id="Re3e8b4bf065b459b"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R18477e5145584d7b"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R4910903c19954c88"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1107,7 +1107,7 @@
         <f>"预算 "&amp;TEXT($D$52,"0%")&amp;" 理论资金"</f>
       </c>
       <c r="D22" s="65">
-        <f>IF($D$51&lt;&gt;"可达","",$J$41+IF($G$40="pons",$G$50/$J$51-$G$49,IF($G$40="four-stock",($G$50/$J$50-$G$49)/(1-$G$42),($G$50/$J$50-$G$49)*(1+$G$42))))</f>
+        <f>IF($D$51&lt;&gt;"可达","",$J$41+IF($G$40="pons",($G$50/$J$51-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",($G$50/$J$50-$G$49)/(1-$G$42),($G$50/$J$50-$G$49)*(1+$G$42))))</f>
       </c>
       <c r="E22" s="3">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
@@ -1625,7 +1625,7 @@
         <v>预算交换 TOKEN</v>
       </c>
       <c r="J51" s="49">
-        <f>$G$48-MAX(0,($D$52-$G$43)*$D$45)/(1-$G$42-$J$48)</f>
+        <f>$G$48-MAX(0,($D$52-$G$43)*$D$45)</f>
       </c>
       <c r="K51" s="49"/>
       <c r="L51" s="49"/>
@@ -1679,7 +1679,7 @@
         <v>当前控筹上限</v>
       </c>
       <c r="D54" s="58">
-        <f>IF($G$40="pons",MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$48)*$G$48/$D$45),IF(OR($G$40="flap",$G$40="four-stock"),$G$43+(1-$J$46)*$G$48/$D$45,1))</f>
+        <f>IF($G$40="pons",1-$G$51/$D$45,IF(OR($G$40="flap",$G$40="four-stock"),$G$43+(1-$J$46)*$G$48/$D$45,1))</f>
       </c>
       <c r="E54" s="49"/>
       <c r="F54" s="49" t="str">
@@ -2155,7 +2155,7 @@
         <f>IF($G$40="pons",$G$43,80%)</f>
       </c>
       <c r="D72" s="75">
-        <f>IF(OR(NOT(ISNUMBER(C72)),C72&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C72-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C72)),C72&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C72-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72)))))</f>
       </c>
       <c r="E72" s="81">
         <f>IF(D72="","",IF(ABS(C72-$G$43)&lt;0.000001,$G$49,$G$50/D72))</f>
@@ -2179,7 +2179,7 @@
         <f>IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),0,J72*(1+$G$42))</f>
       </c>
       <c r="L72" s="87">
-        <f>IF(D72="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C72-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E72-$G$49)/(1-$G$42),(E72-$G$49)*(1+$G$42))))</f>
+        <f>IF(D72="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C72-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E72-$G$49)/(1-$G$42),(E72-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -2187,7 +2187,7 @@
         <f>IF($G$40="pons",80%+0*0.5%,IF(80.5%+0*0.5%&lt;=100%,80.5%+0*0.5%,""))</f>
       </c>
       <c r="D73" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C73)),C73&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C73)),C73&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C73-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73)))))</f>
       </c>
       <c r="E73" s="82">
         <f>IF(D73="","",IF(ABS(C73-$G$43)&lt;0.000001,$G$49,$G$50/D73))</f>
@@ -2211,7 +2211,7 @@
         <f>IF(D73="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L73-L72,J73*(1+$G$42)))</f>
       </c>
       <c r="L73" s="88">
-        <f>IF(D73="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E73-$G$49)/(1-$G$42),(E73-$G$49)*(1+$G$42))))</f>
+        <f>IF(D73="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C73-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E73-$G$49)/(1-$G$42),(E73-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -2219,7 +2219,7 @@
         <f>IF($G$40="pons",80%+1*0.5%,IF(80.5%+1*0.5%&lt;=100%,80.5%+1*0.5%,""))</f>
       </c>
       <c r="D74" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C74)),C74&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C74)),C74&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C74-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74)))))</f>
       </c>
       <c r="E74" s="82">
         <f>IF(D74="","",IF(ABS(C74-$G$43)&lt;0.000001,$G$49,$G$50/D74))</f>
@@ -2243,7 +2243,7 @@
         <f>IF(D74="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L74-L73,J74*(1+$G$42)))</f>
       </c>
       <c r="L74" s="88">
-        <f>IF(D74="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E74-$G$49)/(1-$G$42),(E74-$G$49)*(1+$G$42))))</f>
+        <f>IF(D74="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C74-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E74-$G$49)/(1-$G$42),(E74-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -2251,7 +2251,7 @@
         <f>IF($G$40="pons",80%+2*0.5%,IF(80.5%+2*0.5%&lt;=100%,80.5%+2*0.5%,""))</f>
       </c>
       <c r="D75" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C75)),C75&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C75)),C75&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C75-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75)))))</f>
       </c>
       <c r="E75" s="82">
         <f>IF(D75="","",IF(ABS(C75-$G$43)&lt;0.000001,$G$49,$G$50/D75))</f>
@@ -2275,7 +2275,7 @@
         <f>IF(D75="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L75-L74,J75*(1+$G$42)))</f>
       </c>
       <c r="L75" s="88">
-        <f>IF(D75="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E75-$G$49)/(1-$G$42),(E75-$G$49)*(1+$G$42))))</f>
+        <f>IF(D75="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C75-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E75-$G$49)/(1-$G$42),(E75-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -2283,7 +2283,7 @@
         <f>IF($G$40="pons",80%+3*0.5%,IF(80.5%+3*0.5%&lt;=100%,80.5%+3*0.5%,""))</f>
       </c>
       <c r="D76" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C76)),C76&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C76)),C76&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C76-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76)))))</f>
       </c>
       <c r="E76" s="82">
         <f>IF(D76="","",IF(ABS(C76-$G$43)&lt;0.000001,$G$49,$G$50/D76))</f>
@@ -2307,7 +2307,7 @@
         <f>IF(D76="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L76-L75,J76*(1+$G$42)))</f>
       </c>
       <c r="L76" s="88">
-        <f>IF(D76="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E76-$G$49)/(1-$G$42),(E76-$G$49)*(1+$G$42))))</f>
+        <f>IF(D76="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C76-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E76-$G$49)/(1-$G$42),(E76-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -2315,7 +2315,7 @@
         <f>IF($G$40="pons",80%+4*0.5%,IF(80.5%+4*0.5%&lt;=100%,80.5%+4*0.5%,""))</f>
       </c>
       <c r="D77" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C77)),C77&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C77)),C77&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C77-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77)))))</f>
       </c>
       <c r="E77" s="82">
         <f>IF(D77="","",IF(ABS(C77-$G$43)&lt;0.000001,$G$49,$G$50/D77))</f>
@@ -2339,7 +2339,7 @@
         <f>IF(D77="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L77-L76,J77*(1+$G$42)))</f>
       </c>
       <c r="L77" s="88">
-        <f>IF(D77="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E77-$G$49)/(1-$G$42),(E77-$G$49)*(1+$G$42))))</f>
+        <f>IF(D77="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C77-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E77-$G$49)/(1-$G$42),(E77-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -2347,7 +2347,7 @@
         <f>IF($G$40="pons",80%+5*0.5%,IF(80.5%+5*0.5%&lt;=100%,80.5%+5*0.5%,""))</f>
       </c>
       <c r="D78" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C78)),C78&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C78)),C78&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C78-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78)))))</f>
       </c>
       <c r="E78" s="82">
         <f>IF(D78="","",IF(ABS(C78-$G$43)&lt;0.000001,$G$49,$G$50/D78))</f>
@@ -2371,7 +2371,7 @@
         <f>IF(D78="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L78-L77,J78*(1+$G$42)))</f>
       </c>
       <c r="L78" s="88">
-        <f>IF(D78="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E78-$G$49)/(1-$G$42),(E78-$G$49)*(1+$G$42))))</f>
+        <f>IF(D78="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C78-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E78-$G$49)/(1-$G$42),(E78-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -2379,7 +2379,7 @@
         <f>IF($G$40="pons",80%+6*0.5%,IF(80.5%+6*0.5%&lt;=100%,80.5%+6*0.5%,""))</f>
       </c>
       <c r="D79" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C79)),C79&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C79)),C79&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C79-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79)))))</f>
       </c>
       <c r="E79" s="82">
         <f>IF(D79="","",IF(ABS(C79-$G$43)&lt;0.000001,$G$49,$G$50/D79))</f>
@@ -2403,7 +2403,7 @@
         <f>IF(D79="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L79-L78,J79*(1+$G$42)))</f>
       </c>
       <c r="L79" s="88">
-        <f>IF(D79="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E79-$G$49)/(1-$G$42),(E79-$G$49)*(1+$G$42))))</f>
+        <f>IF(D79="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C79-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E79-$G$49)/(1-$G$42),(E79-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -2411,7 +2411,7 @@
         <f>IF($G$40="pons",80%+7*0.5%,IF(80.5%+7*0.5%&lt;=100%,80.5%+7*0.5%,""))</f>
       </c>
       <c r="D80" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C80)),C80&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C80)),C80&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C80-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80)))))</f>
       </c>
       <c r="E80" s="82">
         <f>IF(D80="","",IF(ABS(C80-$G$43)&lt;0.000001,$G$49,$G$50/D80))</f>
@@ -2435,7 +2435,7 @@
         <f>IF(D80="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L80-L79,J80*(1+$G$42)))</f>
       </c>
       <c r="L80" s="88">
-        <f>IF(D80="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E80-$G$49)/(1-$G$42),(E80-$G$49)*(1+$G$42))))</f>
+        <f>IF(D80="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C80-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E80-$G$49)/(1-$G$42),(E80-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -2443,7 +2443,7 @@
         <f>IF($G$40="pons",80%+8*0.5%,IF(80.5%+8*0.5%&lt;=100%,80.5%+8*0.5%,""))</f>
       </c>
       <c r="D81" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C81)),C81&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C81)),C81&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C81-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81)))))</f>
       </c>
       <c r="E81" s="82">
         <f>IF(D81="","",IF(ABS(C81-$G$43)&lt;0.000001,$G$49,$G$50/D81))</f>
@@ -2467,7 +2467,7 @@
         <f>IF(D81="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L81-L80,J81*(1+$G$42)))</f>
       </c>
       <c r="L81" s="88">
-        <f>IF(D81="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E81-$G$49)/(1-$G$42),(E81-$G$49)*(1+$G$42))))</f>
+        <f>IF(D81="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C81-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E81-$G$49)/(1-$G$42),(E81-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -2475,7 +2475,7 @@
         <f>IF($G$40="pons",80%+9*0.5%,IF(80.5%+9*0.5%&lt;=100%,80.5%+9*0.5%,""))</f>
       </c>
       <c r="D82" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C82)),C82&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C82)),C82&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C82-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82)))))</f>
       </c>
       <c r="E82" s="82">
         <f>IF(D82="","",IF(ABS(C82-$G$43)&lt;0.000001,$G$49,$G$50/D82))</f>
@@ -2499,7 +2499,7 @@
         <f>IF(D82="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L82-L81,J82*(1+$G$42)))</f>
       </c>
       <c r="L82" s="88">
-        <f>IF(D82="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E82-$G$49)/(1-$G$42),(E82-$G$49)*(1+$G$42))))</f>
+        <f>IF(D82="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C82-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E82-$G$49)/(1-$G$42),(E82-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -2507,7 +2507,7 @@
         <f>IF($G$40="pons",80%+10*0.5%,IF(80.5%+10*0.5%&lt;=100%,80.5%+10*0.5%,""))</f>
       </c>
       <c r="D83" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C83)),C83&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C83)),C83&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C83-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83)))))</f>
       </c>
       <c r="E83" s="82">
         <f>IF(D83="","",IF(ABS(C83-$G$43)&lt;0.000001,$G$49,$G$50/D83))</f>
@@ -2531,7 +2531,7 @@
         <f>IF(D83="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L83-L82,J83*(1+$G$42)))</f>
       </c>
       <c r="L83" s="88">
-        <f>IF(D83="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E83-$G$49)/(1-$G$42),(E83-$G$49)*(1+$G$42))))</f>
+        <f>IF(D83="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C83-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E83-$G$49)/(1-$G$42),(E83-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -2539,7 +2539,7 @@
         <f>IF($G$40="pons",80%+11*0.5%,IF(80.5%+11*0.5%&lt;=100%,80.5%+11*0.5%,""))</f>
       </c>
       <c r="D84" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C84)),C84&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C84)),C84&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C84-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84)))))</f>
       </c>
       <c r="E84" s="82">
         <f>IF(D84="","",IF(ABS(C84-$G$43)&lt;0.000001,$G$49,$G$50/D84))</f>
@@ -2563,7 +2563,7 @@
         <f>IF(D84="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L84-L83,J84*(1+$G$42)))</f>
       </c>
       <c r="L84" s="88">
-        <f>IF(D84="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E84-$G$49)/(1-$G$42),(E84-$G$49)*(1+$G$42))))</f>
+        <f>IF(D84="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C84-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E84-$G$49)/(1-$G$42),(E84-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -2571,7 +2571,7 @@
         <f>IF($G$40="pons",80%+12*0.5%,IF(80.5%+12*0.5%&lt;=100%,80.5%+12*0.5%,""))</f>
       </c>
       <c r="D85" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C85)),C85&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C85)),C85&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C85-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85)))))</f>
       </c>
       <c r="E85" s="82">
         <f>IF(D85="","",IF(ABS(C85-$G$43)&lt;0.000001,$G$49,$G$50/D85))</f>
@@ -2595,7 +2595,7 @@
         <f>IF(D85="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L85-L84,J85*(1+$G$42)))</f>
       </c>
       <c r="L85" s="88">
-        <f>IF(D85="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E85-$G$49)/(1-$G$42),(E85-$G$49)*(1+$G$42))))</f>
+        <f>IF(D85="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C85-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E85-$G$49)/(1-$G$42),(E85-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -2603,7 +2603,7 @@
         <f>IF($G$40="pons",80%+13*0.5%,IF(80.5%+13*0.5%&lt;=100%,80.5%+13*0.5%,""))</f>
       </c>
       <c r="D86" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C86)),C86&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C86-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C86)),C86&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C86-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86)))))</f>
       </c>
       <c r="E86" s="82">
         <f>IF(D86="","",IF(ABS(C86-$G$43)&lt;0.000001,$G$49,$G$50/D86))</f>
@@ -2627,7 +2627,7 @@
         <f>IF(D86="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L86-L85,J86*(1+$G$42)))</f>
       </c>
       <c r="L86" s="88">
-        <f>IF(D86="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C86-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E86-$G$49)/(1-$G$42),(E86-$G$49)*(1+$G$42))))</f>
+        <f>IF(D86="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C86-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E86-$G$49)/(1-$G$42),(E86-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -2635,7 +2635,7 @@
         <f>IF($G$40="pons",80%+14*0.5%,IF(80.5%+14*0.5%&lt;=100%,80.5%+14*0.5%,""))</f>
       </c>
       <c r="D87" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C87)),C87&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C87-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C87)),C87&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C87-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87)))))</f>
       </c>
       <c r="E87" s="82">
         <f>IF(D87="","",IF(ABS(C87-$G$43)&lt;0.000001,$G$49,$G$50/D87))</f>
@@ -2659,7 +2659,7 @@
         <f>IF(D87="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L87-L86,J87*(1+$G$42)))</f>
       </c>
       <c r="L87" s="88">
-        <f>IF(D87="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C87-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E87-$G$49)/(1-$G$42),(E87-$G$49)*(1+$G$42))))</f>
+        <f>IF(D87="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C87-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E87-$G$49)/(1-$G$42),(E87-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -2667,7 +2667,7 @@
         <f>IF($G$40="pons",80%+15*0.5%,IF(80.5%+15*0.5%&lt;=100%,80.5%+15*0.5%,""))</f>
       </c>
       <c r="D88" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C88)),C88&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C88-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C88)),C88&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C88-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88)))))</f>
       </c>
       <c r="E88" s="82">
         <f>IF(D88="","",IF(ABS(C88-$G$43)&lt;0.000001,$G$49,$G$50/D88))</f>
@@ -2691,7 +2691,7 @@
         <f>IF(D88="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L88-L87,J88*(1+$G$42)))</f>
       </c>
       <c r="L88" s="88">
-        <f>IF(D88="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C88-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E88-$G$49)/(1-$G$42),(E88-$G$49)*(1+$G$42))))</f>
+        <f>IF(D88="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C88-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E88-$G$49)/(1-$G$42),(E88-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -2699,7 +2699,7 @@
         <f>IF($G$40="pons",80%+16*0.5%,IF(80.5%+16*0.5%&lt;=100%,80.5%+16*0.5%,""))</f>
       </c>
       <c r="D89" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C89)),C89&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C89-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C89)),C89&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C89-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89)))))</f>
       </c>
       <c r="E89" s="82">
         <f>IF(D89="","",IF(ABS(C89-$G$43)&lt;0.000001,$G$49,$G$50/D89))</f>
@@ -2723,7 +2723,7 @@
         <f>IF(D89="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L89-L88,J89*(1+$G$42)))</f>
       </c>
       <c r="L89" s="88">
-        <f>IF(D89="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C89-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E89-$G$49)/(1-$G$42),(E89-$G$49)*(1+$G$42))))</f>
+        <f>IF(D89="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C89-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E89-$G$49)/(1-$G$42),(E89-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -2731,7 +2731,7 @@
         <f>IF($G$40="pons",80%+17*0.5%,IF(80.5%+17*0.5%&lt;=100%,80.5%+17*0.5%,""))</f>
       </c>
       <c r="D90" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C90)),C90&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C90-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C90)),C90&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C90-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90)))))</f>
       </c>
       <c r="E90" s="82">
         <f>IF(D90="","",IF(ABS(C90-$G$43)&lt;0.000001,$G$49,$G$50/D90))</f>
@@ -2755,7 +2755,7 @@
         <f>IF(D90="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L90-L89,J90*(1+$G$42)))</f>
       </c>
       <c r="L90" s="88">
-        <f>IF(D90="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C90-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E90-$G$49)/(1-$G$42),(E90-$G$49)*(1+$G$42))))</f>
+        <f>IF(D90="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C90-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E90-$G$49)/(1-$G$42),(E90-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -2763,7 +2763,7 @@
         <f>IF($G$40="pons",80%+18*0.5%,IF(80.5%+18*0.5%&lt;=100%,80.5%+18*0.5%,""))</f>
       </c>
       <c r="D91" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C91)),C91&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C91-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C91)),C91&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C91-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91)))))</f>
       </c>
       <c r="E91" s="82">
         <f>IF(D91="","",IF(ABS(C91-$G$43)&lt;0.000001,$G$49,$G$50/D91))</f>
@@ -2787,7 +2787,7 @@
         <f>IF(D91="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L91-L90,J91*(1+$G$42)))</f>
       </c>
       <c r="L91" s="88">
-        <f>IF(D91="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C91-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E91-$G$49)/(1-$G$42),(E91-$G$49)*(1+$G$42))))</f>
+        <f>IF(D91="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C91-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E91-$G$49)/(1-$G$42),(E91-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -2795,7 +2795,7 @@
         <f>IF($G$40="pons",80%+19*0.5%,IF(80.5%+19*0.5%&lt;=100%,80.5%+19*0.5%,""))</f>
       </c>
       <c r="D92" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C92)),C92&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C92-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C92)),C92&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C92-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92)))))</f>
       </c>
       <c r="E92" s="82">
         <f>IF(D92="","",IF(ABS(C92-$G$43)&lt;0.000001,$G$49,$G$50/D92))</f>
@@ -2819,7 +2819,7 @@
         <f>IF(D92="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L92-L91,J92*(1+$G$42)))</f>
       </c>
       <c r="L92" s="88">
-        <f>IF(D92="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C92-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E92-$G$49)/(1-$G$42),(E92-$G$49)*(1+$G$42))))</f>
+        <f>IF(D92="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C92-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E92-$G$49)/(1-$G$42),(E92-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -2827,7 +2827,7 @@
         <f>IF($G$40="pons",80%+20*0.5%,IF(80.5%+20*0.5%&lt;=100%,80.5%+20*0.5%,""))</f>
       </c>
       <c r="D93" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C93)),C93&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C93-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C93)),C93&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C93-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93)))))</f>
       </c>
       <c r="E93" s="82">
         <f>IF(D93="","",IF(ABS(C93-$G$43)&lt;0.000001,$G$49,$G$50/D93))</f>
@@ -2851,7 +2851,7 @@
         <f>IF(D93="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L93-L92,J93*(1+$G$42)))</f>
       </c>
       <c r="L93" s="88">
-        <f>IF(D93="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C93-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E93-$G$49)/(1-$G$42),(E93-$G$49)*(1+$G$42))))</f>
+        <f>IF(D93="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C93-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E93-$G$49)/(1-$G$42),(E93-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -2859,7 +2859,7 @@
         <f>IF($G$40="pons",80%+21*0.5%,IF(80.5%+21*0.5%&lt;=100%,80.5%+21*0.5%,""))</f>
       </c>
       <c r="D94" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C94)),C94&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C94-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C94)),C94&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C94-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94)))))</f>
       </c>
       <c r="E94" s="82">
         <f>IF(D94="","",IF(ABS(C94-$G$43)&lt;0.000001,$G$49,$G$50/D94))</f>
@@ -2883,7 +2883,7 @@
         <f>IF(D94="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L94-L93,J94*(1+$G$42)))</f>
       </c>
       <c r="L94" s="88">
-        <f>IF(D94="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C94-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E94-$G$49)/(1-$G$42),(E94-$G$49)*(1+$G$42))))</f>
+        <f>IF(D94="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C94-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E94-$G$49)/(1-$G$42),(E94-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -2891,7 +2891,7 @@
         <f>IF($G$40="pons",80%+22*0.5%,IF(80.5%+22*0.5%&lt;=100%,80.5%+22*0.5%,""))</f>
       </c>
       <c r="D95" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C95)),C95&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C95-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C95)),C95&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C95-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95)))))</f>
       </c>
       <c r="E95" s="82">
         <f>IF(D95="","",IF(ABS(C95-$G$43)&lt;0.000001,$G$49,$G$50/D95))</f>
@@ -2915,7 +2915,7 @@
         <f>IF(D95="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L95-L94,J95*(1+$G$42)))</f>
       </c>
       <c r="L95" s="88">
-        <f>IF(D95="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C95-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E95-$G$49)/(1-$G$42),(E95-$G$49)*(1+$G$42))))</f>
+        <f>IF(D95="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C95-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E95-$G$49)/(1-$G$42),(E95-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -2923,7 +2923,7 @@
         <f>IF($G$40="pons",80%+23*0.5%,IF(80.5%+23*0.5%&lt;=100%,80.5%+23*0.5%,""))</f>
       </c>
       <c r="D96" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C96)),C96&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C96-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C96)),C96&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C96-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96)))))</f>
       </c>
       <c r="E96" s="82">
         <f>IF(D96="","",IF(ABS(C96-$G$43)&lt;0.000001,$G$49,$G$50/D96))</f>
@@ -2947,7 +2947,7 @@
         <f>IF(D96="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L96-L95,J96*(1+$G$42)))</f>
       </c>
       <c r="L96" s="88">
-        <f>IF(D96="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C96-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E96-$G$49)/(1-$G$42),(E96-$G$49)*(1+$G$42))))</f>
+        <f>IF(D96="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C96-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E96-$G$49)/(1-$G$42),(E96-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -2955,7 +2955,7 @@
         <f>IF($G$40="pons",80%+24*0.5%,IF(80.5%+24*0.5%&lt;=100%,80.5%+24*0.5%,""))</f>
       </c>
       <c r="D97" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C97)),C97&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C97-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C97)),C97&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C97-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97)))))</f>
       </c>
       <c r="E97" s="82">
         <f>IF(D97="","",IF(ABS(C97-$G$43)&lt;0.000001,$G$49,$G$50/D97))</f>
@@ -2979,7 +2979,7 @@
         <f>IF(D97="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L97-L96,J97*(1+$G$42)))</f>
       </c>
       <c r="L97" s="88">
-        <f>IF(D97="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C97-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E97-$G$49)/(1-$G$42),(E97-$G$49)*(1+$G$42))))</f>
+        <f>IF(D97="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C97-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E97-$G$49)/(1-$G$42),(E97-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -2987,7 +2987,7 @@
         <f>IF($G$40="pons",80%+25*0.5%,IF(80.5%+25*0.5%&lt;=100%,80.5%+25*0.5%,""))</f>
       </c>
       <c r="D98" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C98)),C98&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C98-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C98)),C98&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C98-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98)))))</f>
       </c>
       <c r="E98" s="82">
         <f>IF(D98="","",IF(ABS(C98-$G$43)&lt;0.000001,$G$49,$G$50/D98))</f>
@@ -3011,7 +3011,7 @@
         <f>IF(D98="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L98-L97,J98*(1+$G$42)))</f>
       </c>
       <c r="L98" s="88">
-        <f>IF(D98="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C98-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E98-$G$49)/(1-$G$42),(E98-$G$49)*(1+$G$42))))</f>
+        <f>IF(D98="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C98-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E98-$G$49)/(1-$G$42),(E98-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3019,7 +3019,7 @@
         <f>IF($G$40="pons",80%+26*0.5%,IF(80.5%+26*0.5%&lt;=100%,80.5%+26*0.5%,""))</f>
       </c>
       <c r="D99" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C99)),C99&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C99-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C99)),C99&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C99-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99)))))</f>
       </c>
       <c r="E99" s="82">
         <f>IF(D99="","",IF(ABS(C99-$G$43)&lt;0.000001,$G$49,$G$50/D99))</f>
@@ -3043,7 +3043,7 @@
         <f>IF(D99="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L99-L98,J99*(1+$G$42)))</f>
       </c>
       <c r="L99" s="88">
-        <f>IF(D99="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C99-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E99-$G$49)/(1-$G$42),(E99-$G$49)*(1+$G$42))))</f>
+        <f>IF(D99="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C99-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E99-$G$49)/(1-$G$42),(E99-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3051,7 +3051,7 @@
         <f>IF($G$40="pons",80%+27*0.5%,IF(80.5%+27*0.5%&lt;=100%,80.5%+27*0.5%,""))</f>
       </c>
       <c r="D100" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C100)),C100&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C100-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C100)),C100&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C100-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100)))))</f>
       </c>
       <c r="E100" s="82">
         <f>IF(D100="","",IF(ABS(C100-$G$43)&lt;0.000001,$G$49,$G$50/D100))</f>
@@ -3075,7 +3075,7 @@
         <f>IF(D100="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L100-L99,J100*(1+$G$42)))</f>
       </c>
       <c r="L100" s="88">
-        <f>IF(D100="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C100-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E100-$G$49)/(1-$G$42),(E100-$G$49)*(1+$G$42))))</f>
+        <f>IF(D100="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C100-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E100-$G$49)/(1-$G$42),(E100-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3083,7 +3083,7 @@
         <f>IF($G$40="pons",80%+28*0.5%,IF(80.5%+28*0.5%&lt;=100%,80.5%+28*0.5%,""))</f>
       </c>
       <c r="D101" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C101)),C101&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C101-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C101)),C101&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C101-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101)))))</f>
       </c>
       <c r="E101" s="82">
         <f>IF(D101="","",IF(ABS(C101-$G$43)&lt;0.000001,$G$49,$G$50/D101))</f>
@@ -3107,7 +3107,7 @@
         <f>IF(D101="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L101-L100,J101*(1+$G$42)))</f>
       </c>
       <c r="L101" s="88">
-        <f>IF(D101="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C101-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E101-$G$49)/(1-$G$42),(E101-$G$49)*(1+$G$42))))</f>
+        <f>IF(D101="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C101-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E101-$G$49)/(1-$G$42),(E101-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3115,7 +3115,7 @@
         <f>IF($G$40="pons",80%+29*0.5%,IF(80.5%+29*0.5%&lt;=100%,80.5%+29*0.5%,""))</f>
       </c>
       <c r="D102" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C102)),C102&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C102-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C102)),C102&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C102-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102)))))</f>
       </c>
       <c r="E102" s="82">
         <f>IF(D102="","",IF(ABS(C102-$G$43)&lt;0.000001,$G$49,$G$50/D102))</f>
@@ -3139,7 +3139,7 @@
         <f>IF(D102="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L102-L101,J102*(1+$G$42)))</f>
       </c>
       <c r="L102" s="88">
-        <f>IF(D102="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C102-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E102-$G$49)/(1-$G$42),(E102-$G$49)*(1+$G$42))))</f>
+        <f>IF(D102="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C102-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E102-$G$49)/(1-$G$42),(E102-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -3147,7 +3147,7 @@
         <f>IF($G$40="pons",80%+30*0.5%,IF(80.5%+30*0.5%&lt;=100%,80.5%+30*0.5%,""))</f>
       </c>
       <c r="D103" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C103)),C103&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C103-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C103)),C103&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C103-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103)))))</f>
       </c>
       <c r="E103" s="82">
         <f>IF(D103="","",IF(ABS(C103-$G$43)&lt;0.000001,$G$49,$G$50/D103))</f>
@@ -3171,7 +3171,7 @@
         <f>IF(D103="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L103-L102,J103*(1+$G$42)))</f>
       </c>
       <c r="L103" s="88">
-        <f>IF(D103="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C103-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E103-$G$49)/(1-$G$42),(E103-$G$49)*(1+$G$42))))</f>
+        <f>IF(D103="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C103-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E103-$G$49)/(1-$G$42),(E103-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3179,7 +3179,7 @@
         <f>IF($G$40="pons",80%+31*0.5%,IF(80.5%+31*0.5%&lt;=100%,80.5%+31*0.5%,""))</f>
       </c>
       <c r="D104" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C104)),C104&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C104-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C104)),C104&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C104-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104)))))</f>
       </c>
       <c r="E104" s="82">
         <f>IF(D104="","",IF(ABS(C104-$G$43)&lt;0.000001,$G$49,$G$50/D104))</f>
@@ -3203,7 +3203,7 @@
         <f>IF(D104="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L104-L103,J104*(1+$G$42)))</f>
       </c>
       <c r="L104" s="88">
-        <f>IF(D104="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C104-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E104-$G$49)/(1-$G$42),(E104-$G$49)*(1+$G$42))))</f>
+        <f>IF(D104="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C104-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E104-$G$49)/(1-$G$42),(E104-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3211,7 +3211,7 @@
         <f>IF($G$40="pons",80%+32*0.5%,IF(80.5%+32*0.5%&lt;=100%,80.5%+32*0.5%,""))</f>
       </c>
       <c r="D105" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C105)),C105&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C105-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C105)),C105&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C105-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105)))))</f>
       </c>
       <c r="E105" s="82">
         <f>IF(D105="","",IF(ABS(C105-$G$43)&lt;0.000001,$G$49,$G$50/D105))</f>
@@ -3235,7 +3235,7 @@
         <f>IF(D105="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L105-L104,J105*(1+$G$42)))</f>
       </c>
       <c r="L105" s="88">
-        <f>IF(D105="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C105-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E105-$G$49)/(1-$G$42),(E105-$G$49)*(1+$G$42))))</f>
+        <f>IF(D105="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C105-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E105-$G$49)/(1-$G$42),(E105-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3243,7 +3243,7 @@
         <f>IF($G$40="pons",80%+33*0.5%,IF(80.5%+33*0.5%&lt;=100%,80.5%+33*0.5%,""))</f>
       </c>
       <c r="D106" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C106)),C106&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C106-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C106)),C106&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C106-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106)))))</f>
       </c>
       <c r="E106" s="82">
         <f>IF(D106="","",IF(ABS(C106-$G$43)&lt;0.000001,$G$49,$G$50/D106))</f>
@@ -3267,7 +3267,7 @@
         <f>IF(D106="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L106-L105,J106*(1+$G$42)))</f>
       </c>
       <c r="L106" s="88">
-        <f>IF(D106="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C106-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E106-$G$49)/(1-$G$42),(E106-$G$49)*(1+$G$42))))</f>
+        <f>IF(D106="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C106-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E106-$G$49)/(1-$G$42),(E106-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3275,7 +3275,7 @@
         <f>IF($G$40="pons",80%+34*0.5%,IF(80.5%+34*0.5%&lt;=100%,80.5%+34*0.5%,""))</f>
       </c>
       <c r="D107" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C107)),C107&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C107-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C107)),C107&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C107-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107)))))</f>
       </c>
       <c r="E107" s="82">
         <f>IF(D107="","",IF(ABS(C107-$G$43)&lt;0.000001,$G$49,$G$50/D107))</f>
@@ -3299,7 +3299,7 @@
         <f>IF(D107="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L107-L106,J107*(1+$G$42)))</f>
       </c>
       <c r="L107" s="88">
-        <f>IF(D107="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C107-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E107-$G$49)/(1-$G$42),(E107-$G$49)*(1+$G$42))))</f>
+        <f>IF(D107="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C107-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E107-$G$49)/(1-$G$42),(E107-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3307,7 +3307,7 @@
         <f>IF($G$40="pons",80%+35*0.5%,IF(80.5%+35*0.5%&lt;=100%,80.5%+35*0.5%,""))</f>
       </c>
       <c r="D108" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C108)),C108&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C108-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C108)),C108&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C108-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108)))))</f>
       </c>
       <c r="E108" s="82">
         <f>IF(D108="","",IF(ABS(C108-$G$43)&lt;0.000001,$G$49,$G$50/D108))</f>
@@ -3331,7 +3331,7 @@
         <f>IF(D108="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L108-L107,J108*(1+$G$42)))</f>
       </c>
       <c r="L108" s="88">
-        <f>IF(D108="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C108-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E108-$G$49)/(1-$G$42),(E108-$G$49)*(1+$G$42))))</f>
+        <f>IF(D108="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C108-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E108-$G$49)/(1-$G$42),(E108-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -3339,7 +3339,7 @@
         <f>IF($G$40="pons",80%+36*0.5%,IF(80.5%+36*0.5%&lt;=100%,80.5%+36*0.5%,""))</f>
       </c>
       <c r="D109" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C109)),C109&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C109-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C109)),C109&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C109-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109)))))</f>
       </c>
       <c r="E109" s="82">
         <f>IF(D109="","",IF(ABS(C109-$G$43)&lt;0.000001,$G$49,$G$50/D109))</f>
@@ -3363,7 +3363,7 @@
         <f>IF(D109="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L109-L108,J109*(1+$G$42)))</f>
       </c>
       <c r="L109" s="88">
-        <f>IF(D109="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C109-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E109-$G$49)/(1-$G$42),(E109-$G$49)*(1+$G$42))))</f>
+        <f>IF(D109="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C109-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E109-$G$49)/(1-$G$42),(E109-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3371,7 +3371,7 @@
         <f>IF($G$40="pons",80%+37*0.5%,IF(80.5%+37*0.5%&lt;=100%,80.5%+37*0.5%,""))</f>
       </c>
       <c r="D110" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C110)),C110&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C110-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C110)),C110&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C110-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110)))))</f>
       </c>
       <c r="E110" s="82">
         <f>IF(D110="","",IF(ABS(C110-$G$43)&lt;0.000001,$G$49,$G$50/D110))</f>
@@ -3395,7 +3395,7 @@
         <f>IF(D110="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L110-L109,J110*(1+$G$42)))</f>
       </c>
       <c r="L110" s="88">
-        <f>IF(D110="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C110-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E110-$G$49)/(1-$G$42),(E110-$G$49)*(1+$G$42))))</f>
+        <f>IF(D110="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C110-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E110-$G$49)/(1-$G$42),(E110-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3403,7 +3403,7 @@
         <f>IF($G$40="pons",80%+38*0.5%,IF(80.5%+38*0.5%&lt;=100%,80.5%+38*0.5%,""))</f>
       </c>
       <c r="D111" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C111)),C111&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C111-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C111)),C111&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C111-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111)))))</f>
       </c>
       <c r="E111" s="82">
         <f>IF(D111="","",IF(ABS(C111-$G$43)&lt;0.000001,$G$49,$G$50/D111))</f>
@@ -3427,7 +3427,7 @@
         <f>IF(D111="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L111-L110,J111*(1+$G$42)))</f>
       </c>
       <c r="L111" s="88">
-        <f>IF(D111="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C111-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E111-$G$49)/(1-$G$42),(E111-$G$49)*(1+$G$42))))</f>
+        <f>IF(D111="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C111-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E111-$G$49)/(1-$G$42),(E111-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3435,7 +3435,7 @@
         <f>IF($G$40="pons",80%+39*0.5%,IF(80.5%+39*0.5%&lt;=100%,80.5%+39*0.5%,""))</f>
       </c>
       <c r="D112" s="76">
-        <f>IF(OR(NOT(ISNUMBER(C112)),C112&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C112-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C112)),C112&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C112-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112)))))</f>
       </c>
       <c r="E112" s="82">
         <f>IF(D112="","",IF(ABS(C112-$G$43)&lt;0.000001,$G$49,$G$50/D112))</f>
@@ -3459,7 +3459,7 @@
         <f>IF(D112="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L112-L111,J112*(1+$G$42)))</f>
       </c>
       <c r="L112" s="88">
-        <f>IF(D112="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C112-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E112-$G$49)/(1-$G$42),(E112-$G$49)*(1+$G$42))))</f>
+        <f>IF(D112="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C112-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E112-$G$49)/(1-$G$42),(E112-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3467,7 +3467,7 @@
         <f>IF($G$40="pons",80%+40*0.5%,IF(80.5%+40*0.5%&lt;=100%,80.5%+40*0.5%,""))</f>
       </c>
       <c r="D113" s="77">
-        <f>IF(OR(NOT(ISNUMBER(C113)),C113&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C113-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C113)),C113&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C113-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113)))))</f>
       </c>
       <c r="E113" s="83">
         <f>IF(D113="","",IF(ABS(C113-$G$43)&lt;0.000001,$G$49,$G$50/D113))</f>
@@ -3491,7 +3491,7 @@
         <f>IF(D113="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L113-L112,J113*(1+$G$42)))</f>
       </c>
       <c r="L113" s="89">
-        <f>IF(D113="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C113-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E113-$G$49)/(1-$G$42),(E113-$G$49)*(1+$G$42))))</f>
+        <f>IF(D113="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C113-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E113-$G$49)/(1-$G$42),(E113-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="114" ht="6" customHeight="1">

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R18477e5145584d7b"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R4910903c19954c88"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R9628a35141504f93"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R3db615e523e9497d"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -825,7 +825,7 @@
         <v>平台 / Quote</v>
       </c>
       <c r="D7" s="67" t="str">
-        <v>Four.meme / BNB</v>
+        <v>Pons V2 / USDG</v>
       </c>
       <c r="E7" s="67"/>
       <c r="F7" s="49" t="str">
@@ -839,7 +839,7 @@
         <v>买入税率（Flap）</v>
       </c>
       <c r="J7" s="55">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,25,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,25,FALSE)</f>
       </c>
       <c r="K7" s="49"/>
       <c r="L7" s="49"/>
@@ -849,7 +849,7 @@
         <v>目标控筹率</v>
       </c>
       <c r="D8" s="55" t="n">
-        <v>0.94</v>
+        <v>0.9</v>
       </c>
       <c r="E8" s="49"/>
       <c r="F8" s="49" t="str">
@@ -863,7 +863,7 @@
         <v>卖出税率（Flap）</v>
       </c>
       <c r="J8" s="55">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,26,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,26,FALSE)</f>
       </c>
       <c r="K8" s="49"/>
       <c r="L8" s="49"/>
@@ -885,7 +885,7 @@
         <v>Creator Tax（Pons）</v>
       </c>
       <c r="J9" s="55">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,27,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,27,FALSE)</f>
       </c>
       <c r="K9" s="49"/>
       <c r="L9" s="49"/>
@@ -924,7 +924,7 @@
         <v>单地址 Gas</v>
       </c>
       <c r="G11" s="54">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,33,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,33,FALSE)</f>
       </c>
       <c r="H11" s="49"/>
       <c r="I11" s="49"/>
@@ -951,7 +951,7 @@
         <v>洗筹基础费率</v>
       </c>
       <c r="J12" s="55">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,20,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,20,FALSE)</f>
       </c>
       <c r="K12" s="49"/>
       <c r="L12" s="49"/>
@@ -1028,7 +1028,7 @@
         <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
       </c>
       <c r="E18" s="48">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
       </c>
       <c r="F18" s="3" t="str">
         <v>原生币 Gas 储备</v>
@@ -1037,7 +1037,7 @@
         <f>D53*MAX(0,G11)</f>
       </c>
       <c r="H18" s="48">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,4,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,4,FALSE)</f>
       </c>
       <c r="I18" s="3" t="str">
         <v>总折算 / USDT</v>
@@ -1110,7 +1110,7 @@
         <f>IF($D$51&lt;&gt;"可达","",$J$41+IF($G$40="pons",($G$50/$J$51-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",($G$50/$J$50-$G$49)/(1-$G$42),($G$50/$J$50-$G$49)*(1+$G$42))))</f>
       </c>
       <c r="E22" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -1130,7 +1130,7 @@
         <f>IF($D$51="可达",$J$41*MAX(0,$G$7-1),"")</f>
       </c>
       <c r="E23" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -1152,7 +1152,7 @@
         <f>IF($D$51="可达",$J$52*$D$29,"")</f>
       </c>
       <c r="E24" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -1174,7 +1174,7 @@
         <f>IF($D$51="可达",$G$12,"")</f>
       </c>
       <c r="E25" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -1193,10 +1193,10 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="65">
-        <f>IF($D$51&lt;&gt;"可达","",IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,34,FALSE)="quote",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*IF($G$40="pons",1,IF($G$40="four-stock",1/(1-$G$42),1+$G$42))),"")))</f>
+        <f>IF($D$51&lt;&gt;"可达","",IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,34,FALSE)="quote",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*IF($G$40="pons",1,IF($G$40="four-stock",1/(1-$G$42),1+$G$42))),"")))</f>
       </c>
       <c r="E26" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -1280,7 +1280,7 @@
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" ht="20" customHeight="1" hidden="1">
+    <row r="31" ht="20" hidden="1" customHeight="1">
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31"/>
@@ -1292,7 +1292,7 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" ht="20" customHeight="1" hidden="1">
+    <row r="32" ht="20" hidden="1" customHeight="1">
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32"/>
@@ -1304,7 +1304,7 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" ht="20" customHeight="1" hidden="1">
+    <row r="33" ht="20" hidden="1" customHeight="1">
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
@@ -1316,7 +1316,7 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" ht="20" customHeight="1" hidden="1">
+    <row r="34" ht="20" hidden="1" customHeight="1">
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
@@ -1328,7 +1328,7 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" ht="20" customHeight="1" hidden="1">
+    <row r="35" ht="20" hidden="1" customHeight="1">
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35"/>
@@ -1362,10 +1362,10 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="65">
-        <f>IF($G$40="four-stock",E126,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,23,FALSE))</f>
+        <f>IF($G$40="four-stock",E126,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,23,FALSE))</f>
       </c>
       <c r="H37" s="3">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
@@ -1398,7 +1398,7 @@
       <c r="K39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="40" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C40" s="49"/>
       <c r="D40" s="49"/>
       <c r="E40" s="49"/>
@@ -1406,7 +1406,7 @@
         <v>模型类型</v>
       </c>
       <c r="G40" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,10,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,10,FALSE)</f>
       </c>
       <c r="H40" s="49"/>
       <c r="I40" s="49"/>
@@ -1414,7 +1414,7 @@
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
     </row>
-    <row r="41" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="41" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C41" s="49"/>
       <c r="D41" s="49"/>
       <c r="E41" s="49"/>
@@ -1422,7 +1422,7 @@
         <v>内盘基础费</v>
       </c>
       <c r="G41" s="58">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,19,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,19,FALSE)</f>
       </c>
       <c r="H41" s="49"/>
       <c r="I41" s="49" t="str">
@@ -1434,7 +1434,7 @@
       <c r="K41" s="49"/>
       <c r="L41" s="49"/>
     </row>
-    <row r="42" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="42" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C42" s="49"/>
       <c r="D42" s="49"/>
       <c r="E42" s="49"/>
@@ -1442,7 +1442,7 @@
         <v>外盘基础费</v>
       </c>
       <c r="G42" s="58">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,20,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,20,FALSE)</f>
       </c>
       <c r="H42" s="49"/>
       <c r="I42" s="49"/>
@@ -1450,7 +1450,7 @@
       <c r="K42" s="49"/>
       <c r="L42" s="49"/>
     </row>
-    <row r="43" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="43" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C43" s="49"/>
       <c r="D43" s="49"/>
       <c r="E43" s="49"/>
@@ -1458,19 +1458,19 @@
         <v>毕业控筹率</v>
       </c>
       <c r="G43" s="58">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,15,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,15,FALSE)</f>
       </c>
       <c r="H43" s="49"/>
       <c r="I43" s="49" t="str">
         <v>模型键</v>
       </c>
       <c r="J43" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,2,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,2,FALSE)</f>
       </c>
       <c r="K43" s="49"/>
       <c r="L43" s="49"/>
     </row>
-    <row r="44" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="44" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C44" s="49"/>
       <c r="D44" s="49"/>
       <c r="E44" s="49"/>
@@ -1478,43 +1478,43 @@
         <v>内盘初始 TOKEN</v>
       </c>
       <c r="G44" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,12,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,12,FALSE)</f>
       </c>
       <c r="H44" s="49"/>
       <c r="I44" s="49" t="str">
         <v>原生币价格 / USDT</v>
       </c>
       <c r="J44" s="49">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,3,FALSE)=VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,4,FALSE),$D$55,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,7,FALSE))</f>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)=VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,4,FALSE),$D$55,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,7,FALSE))</f>
       </c>
       <c r="K44" s="49"/>
       <c r="L44" s="49"/>
     </row>
-    <row r="45" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="45" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C45" s="49" t="str">
         <v>总供应量</v>
       </c>
       <c r="D45" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,11,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,11,FALSE)</f>
       </c>
       <c r="E45" s="49"/>
       <c r="F45" s="49" t="str">
         <v>内盘初始 Quote</v>
       </c>
       <c r="G45" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,13,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,13,FALSE)</f>
       </c>
       <c r="H45" s="49"/>
       <c r="I45" s="49" t="str">
         <v>税率上限</v>
       </c>
       <c r="J45" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,32,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,32,FALSE)</f>
       </c>
       <c r="K45" s="49"/>
       <c r="L45" s="49"/>
     </row>
-    <row r="46" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="46" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C46" s="49"/>
       <c r="D46" s="49"/>
       <c r="E46" s="49"/>
@@ -1522,7 +1522,7 @@
         <v>内盘 K</v>
       </c>
       <c r="G46" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,14,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,14,FALSE)</f>
       </c>
       <c r="H46" s="49"/>
       <c r="I46" s="49" t="str">
@@ -1534,7 +1534,7 @@
       <c r="K46" s="49"/>
       <c r="L46" s="49"/>
     </row>
-    <row r="47" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="47" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C47" s="49"/>
       <c r="D47" s="49"/>
       <c r="E47" s="49"/>
@@ -1550,7 +1550,7 @@
       <c r="K47" s="49"/>
       <c r="L47" s="49"/>
     </row>
-    <row r="48" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="48" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C48" s="49"/>
       <c r="D48" s="49"/>
       <c r="E48" s="49"/>
@@ -1558,7 +1558,7 @@
         <v>外盘初始 TOKEN</v>
       </c>
       <c r="G48" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,16,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,16,FALSE)</f>
       </c>
       <c r="H48" s="49"/>
       <c r="I48" s="49" t="str">
@@ -1570,7 +1570,7 @@
       <c r="K48" s="49"/>
       <c r="L48" s="49"/>
     </row>
-    <row r="49" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="49" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C49" s="49"/>
       <c r="D49" s="49"/>
       <c r="E49" s="49"/>
@@ -1578,7 +1578,7 @@
         <v>外盘初始 Quote</v>
       </c>
       <c r="G49" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,17,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,17,FALSE)</f>
       </c>
       <c r="H49" s="49"/>
       <c r="I49" s="49"/>
@@ -1586,7 +1586,7 @@
       <c r="K49" s="49"/>
       <c r="L49" s="49"/>
     </row>
-    <row r="50" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="50" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C50" s="49"/>
       <c r="D50" s="49"/>
       <c r="E50" s="49"/>
@@ -1594,7 +1594,7 @@
         <v>外盘 K</v>
       </c>
       <c r="G50" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,18,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,18,FALSE)</f>
       </c>
       <c r="H50" s="49"/>
       <c r="I50" s="49" t="str">
@@ -1606,7 +1606,7 @@
       <c r="K50" s="49"/>
       <c r="L50" s="49"/>
     </row>
-    <row r="51" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="51" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C51" s="49" t="str">
         <v>目标是否可达</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>永久锁仓 TOKEN</v>
       </c>
       <c r="G51" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,22,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,22,FALSE)</f>
       </c>
       <c r="H51" s="49"/>
       <c r="I51" s="49" t="str">
@@ -1630,7 +1630,7 @@
       <c r="K51" s="49"/>
       <c r="L51" s="49"/>
     </row>
-    <row r="52" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="52" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C52" s="49" t="str">
         <v>预算控筹率</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>一套内盘原值</v>
       </c>
       <c r="G52" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,21,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,21,FALSE)</f>
       </c>
       <c r="H52" s="49"/>
       <c r="I52" s="49" t="str">
@@ -1654,7 +1654,7 @@
       <c r="K52" s="49"/>
       <c r="L52" s="49"/>
     </row>
-    <row r="53" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="53" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C53" s="49" t="str">
         <v>地址总数</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>内盘募集 Quote</v>
       </c>
       <c r="G53" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,24,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,24,FALSE)</f>
       </c>
       <c r="H53" s="49"/>
       <c r="I53" s="49"/>
@@ -1674,7 +1674,7 @@
       <c r="K53" s="49"/>
       <c r="L53" s="49"/>
     </row>
-    <row r="54" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="54" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C54" s="49" t="str">
         <v>当前控筹上限</v>
       </c>
@@ -1693,24 +1693,24 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="58">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,34,FALSE)="quote",1,IF($G$40="pons",MAX(0,1-MAX(0,$J$12)-$J$48),(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))))</f>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,34,FALSE)="quote",1,IF($G$40="pons",MAX(0,1-MAX(0,$J$12)-$J$48),(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))))</f>
       </c>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
     </row>
-    <row r="55" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="55" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C55" s="49" t="str">
         <v>有效价格 / USDT</v>
       </c>
       <c r="D55" s="60">
-        <f>IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,IF(AND(ISNUMBER(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,6,FALSE)),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,6,FALSE)&gt;0),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,6,FALSE),""))</f>
+        <f>IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,IF(AND(ISNUMBER(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,6,FALSE)),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,6,FALSE)&gt;0),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,6,FALSE),""))</f>
       </c>
       <c r="E55" s="49"/>
       <c r="F55" s="49" t="str">
         <v>价格来源</v>
       </c>
       <c r="G55" s="49">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,9,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,9,FALSE)</f>
       </c>
       <c r="H55" s="49"/>
       <c r="I55" s="49" t="str">
@@ -1722,12 +1722,12 @@
       <c r="K55" s="49"/>
       <c r="L55" s="49"/>
     </row>
-    <row r="56" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="56" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C56" s="49" t="str">
         <v>价格时间 / UTC</v>
       </c>
       <c r="D56" s="61">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$22,8,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,8,FALSE)</f>
       </c>
       <c r="E56" s="49"/>
       <c r="F56" s="49" t="str">
@@ -4262,7 +4262,7 @@
   </conditionalFormatting>
   <dataValidations count="8">
     <dataValidation type="list" sqref="D7">
-      <formula1>'Quote参数'!$C$14:$C$22</formula1>
+      <formula1>'Quote参数'!$C$14:$C$23</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="D8">
       <formula1>0</formula1>
@@ -5999,6 +5999,122 @@
         <v>https://docs.ponsfamily.com/v2</v>
       </c>
     </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>Pons V2 / USDG</v>
+      </c>
+      <c r="D23" t="str">
+        <v>ponsv2-usdg</v>
+      </c>
+      <c r="E23" t="str">
+        <v>USDG</v>
+      </c>
+      <c r="F23" t="str">
+        <v>ETH</v>
+      </c>
+      <c r="G23" t="str">
+        <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
+      </c>
+      <c r="H23">
+        <v>1.0003961568781237</v>
+      </c>
+      <c r="I23">
+        <v>2580.0817123580937</v>
+      </c>
+      <c r="J23">
+        <v>46285.27349457176</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+        </is>
+      </c>
+      <c r="L23" t="str">
+        <v>pons</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="O23" t="n">
+        <v>202.25</v>
+      </c>
+      <c r="P23" t="n">
+        <v>202250000000</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="R23" t="n">
+        <v>204081632.65306124</v>
+      </c>
+      <c r="S23" t="n">
+        <v>505.625</v>
+      </c>
+      <c r="T23" t="n">
+        <v>103188775510.20409</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>510.7323232323232</v>
+      </c>
+      <c r="X23" t="n">
+        <v>81632653.06122449</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>112.36111111111111</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>505.625</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="str">
+        <v>https://robinhoodchain.blockscout.com/address/0x7eD598BcEf8bd9Edd8C97A195C6d13f40801EC7e?tab=read_contract</v>
+      </c>
+      <c r="AE23" t="str">
+        <v>区块 68,708,148；USDG 6 decimals</v>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AJ23" t="str">
+        <v>quote</v>
+      </c>
+      <c r="AK23" t="str">
+        <v>Pons V2 手续费始终按 Quote leg 计收；Hook 暂存的 Meme 费用会在池内转换回 Quote</v>
+      </c>
+      <c r="AL23" t="str">
+        <v>https://docs.ponsfamily.com/v2</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="C3:M3"/>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R9628a35141504f93"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R3db615e523e9497d"/>
+    <sheet name="控筹模型" sheetId="1" r:id="Refa2ce57623f4d9b"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R9e1971b00c5f408f"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -6039,10 +6039,10 @@
         <v>1000000000</v>
       </c>
       <c r="O23" t="n">
-        <v>202.25</v>
+        <v>3236</v>
       </c>
       <c r="P23" t="n">
-        <v>202250000000</v>
+        <v>3236000000000</v>
       </c>
       <c r="Q23" t="n">
         <v>0.7142857142857143</v>
@@ -6051,10 +6051,10 @@
         <v>204081632.65306124</v>
       </c>
       <c r="S23" t="n">
-        <v>505.625</v>
+        <v>8090</v>
       </c>
       <c r="T23" t="n">
-        <v>103188775510.20409</v>
+        <v>1651020408163.2654</v>
       </c>
       <c r="U23" t="n">
         <v>0.01</v>
@@ -6063,16 +6063,16 @@
         <v>0.01</v>
       </c>
       <c r="W23" t="n">
-        <v>510.7323232323232</v>
+        <v>8171.717171717171</v>
       </c>
       <c r="X23" t="n">
         <v>81632653.06122449</v>
       </c>
       <c r="Y23" t="n">
-        <v>112.36111111111111</v>
+        <v>1797.7777777777778</v>
       </c>
       <c r="Z23" t="n">
-        <v>505.625</v>
+        <v>8090</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -6084,10 +6084,10 @@
         <v>0</v>
       </c>
       <c r="AD23" t="str">
-        <v>https://robinhoodchain.blockscout.com/address/0x7eD598BcEf8bd9Edd8C97A195C6d13f40801EC7e?tab=read_contract</v>
+        <v>https://robin.etherscan.io/tx/0x387e3237904e4822075066331564561c373b691fd47ad2d52b4f64fb4f398c84#eventlog</v>
       </c>
       <c r="AE23" t="str">
-        <v>区块 68,708,148；USDG 6 decimals</v>
+        <v>TRAIN 发行区块 69,045,064；USDG 6 decimals；PERC 迁池同为 8,090</v>
       </c>
       <c r="AF23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="Refa2ce57623f4d9b"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R9e1971b00c5f408f"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R14fcad28f4cb47d3"/>
+    <sheet name="Quote参数" sheetId="2" r:id="Rb0457d51e2684136"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1193,7 +1193,7 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="65">
-        <f>IF($D$51&lt;&gt;"可达","",IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,34,FALSE)="quote",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*IF($G$40="pons",1,IF($G$40="four-stock",1/(1-$G$42),1+$G$42))),"")))</f>
+        <f>IF($D$51&lt;&gt;"可达","",0)</f>
       </c>
       <c r="E26" s="3">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="C28" s="3" t="str">
-        <v>补回目标控筹率</v>
+        <v>原目标控筹率</v>
       </c>
       <c r="D28" s="57">
         <f>D8</f>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="41" t="str">
-        <v>外盘手续费只在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，损耗仍按目标加缓冲 FDV；非逐笔模拟。</v>
+        <v>外盘一卖一买：卖出所得 Quote 全额用于回买，不额外补 Quote。洗后控筹按卖出、买入两腿含税费率同价估算；实际成交量、滑点与价格冲击未计入。洗筹损耗另按预算 FDV × 双边费率列示。</v>
       </c>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
@@ -1693,7 +1693,7 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="58">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,34,FALSE)="quote",1,IF($G$40="pons",MAX(0,1-MAX(0,$J$12)-$J$48),(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))))</f>
+        <f>MAX(0,1-$J$29)*MAX(0,1-$J$30)</f>
       </c>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -4766,7 +4766,7 @@
         <v>洗筹与补回口径</v>
       </c>
       <c r="D11" s="12" t="str">
-        <v>损耗按目标加缓冲的 FDV × 双边费率。外盘手续费仅在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，非逐笔模拟。</v>
+        <v>外盘一卖一买，卖出所得 Quote 全额用于回买。洗后控筹按双边含税费率同价估算，额外补回预留为 0；洗筹损耗预算另列，不计滑点与冲击。</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R14fcad28f4cb47d3"/>
-    <sheet name="Quote参数" sheetId="2" r:id="Rb0457d51e2684136"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R56ed3c3ed042463c"/>
+    <sheet name="Quote参数" sheetId="2" r:id="Rb7541ef9e6094d02"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1193,7 +1193,7 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="65">
-        <f>IF($D$51&lt;&gt;"可达","",0)</f>
+        <f>IF($D$51&lt;&gt;"可达","",IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*(IF($G$40="pons",1/(1-$G$42-$J$48),IF($G$40="four-stock",1/(1-$G$42),1+$G$42)))),""))</f>
       </c>
       <c r="E26" s="3">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="41" t="str">
-        <v>外盘一卖一买：卖出所得 Quote 全额用于回买，不额外补 Quote。洗后控筹按卖出、买入两腿含税费率同价估算；实际成交量、滑点与价格冲击未计入。洗筹损耗另按预算 FDV × 双边费率列示。</v>
+        <v>外盘一卖一买使用卖出所得 Quote 回买；洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote。洗筹损耗另列；未模拟成交量、滑点与价格冲击。</v>
       </c>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
@@ -1717,7 +1717,7 @@
         <v>目标外盘 TOKEN</v>
       </c>
       <c r="J55" s="49">
-        <f>IF($G$40="pons",$G$48-MAX(0,($D$8-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$8)-$G$51,IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8)))))</f>
+        <f>IF($G$40="pons",$G$48-($D$8-$G$43)*$D$45,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8))))</f>
       </c>
       <c r="K55" s="49"/>
       <c r="L55" s="49"/>
@@ -1741,7 +1741,7 @@
         <v>洗后外盘 TOKEN</v>
       </c>
       <c r="J56" s="49">
-        <f>IF($G$40="pons",$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27)))))</f>
+        <f>IF($G$40="pons",$G$48-($D$27-$G$43)*$D$45,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27))))</f>
       </c>
       <c r="K56" s="49"/>
       <c r="L56" s="49"/>
@@ -4766,7 +4766,7 @@
         <v>洗筹与补回口径</v>
       </c>
       <c r="D11" s="12" t="str">
-        <v>外盘一卖一买，卖出所得 Quote 全额用于回买。洗后控筹按双边含税费率同价估算，额外补回预留为 0；洗筹损耗预算另列，不计滑点与冲击。</v>
+        <v>外盘一卖一买用卖出所得 Quote 回买；洗后持币按双边费率估算，再按外盘曲线和买入费预留恢复目标所需 Quote。洗筹损耗另列。</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999604</v>
+        <v>0.999767</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>108.53297905970763</v>
+        <v>116.50714616505647</v>
       </c>
       <c r="I14" s="20">
-        <v>108.53297905970763</v>
+        <v>116.50714616505647</v>
       </c>
       <c r="J14" s="23">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0003961568781237</v>
+        <v>1.0002330543016522</v>
       </c>
       <c r="I15" s="21">
-        <v>108.53297905970763</v>
+        <v>116.50714616505647</v>
       </c>
       <c r="J15" s="24">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0003961568781237</v>
+        <v>1.0002330543016522</v>
       </c>
       <c r="I16" s="21">
-        <v>752.7981080507881</v>
+        <v>786.293206317072</v>
       </c>
       <c r="J16" s="24">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>752.7981080507881</v>
+        <v>786.293206317072</v>
       </c>
       <c r="I17" s="21">
-        <v>752.7981080507881</v>
+        <v>786.293206317072</v>
       </c>
       <c r="J17" s="24">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7357363515952317</v>
+        <v>0.7310933447493266</v>
       </c>
       <c r="I18" s="21">
-        <v>752.7981080507881</v>
+        <v>786.293206317072</v>
       </c>
       <c r="J18" s="24">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>91.08607008375316</v>
+        <v>93.49178358557545</v>
       </c>
       <c r="I19" s="21">
-        <v>91.08607008375316</v>
+        <v>93.49178358557545</v>
       </c>
       <c r="J19" s="24">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>752.7981080507881</v>
+        <v>786.293206317072</v>
       </c>
       <c r="I20" s="21">
-        <v>752.7981080507881</v>
+        <v>786.293206317072</v>
       </c>
       <c r="J20" s="24">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0003961568781237</v>
+        <v>1.0002330543016522</v>
       </c>
       <c r="I21" s="21">
-        <v>752.7981080507881</v>
+        <v>786.293206317072</v>
       </c>
       <c r="J21" s="24">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2580.0817123580937</v>
+        <v>2727.8255833609232</v>
       </c>
       <c r="I22" s="22">
-        <v>2580.0817123580937</v>
+        <v>2727.8255833609232</v>
       </c>
       <c r="J22" s="25">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0003961568781237</v>
+        <v>1.0002330543016522</v>
       </c>
       <c r="I23">
-        <v>2580.0817123580937</v>
+        <v>2727.8255833609232</v>
       </c>
       <c r="J23">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R56ed3c3ed042463c"/>
-    <sheet name="Quote参数" sheetId="2" r:id="Rb7541ef9e6094d02"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R73381a3b10ae4f3f"/>
+    <sheet name="Quote参数" sheetId="2" r:id="Rc860e189e8394303"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="7">
+  <x:numFmts count="8">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <x:numFmt numFmtId="201" formatCode="0.0000000000"/>
     <x:numFmt numFmtId="202" formatCode="@"/>
@@ -23,6 +23,7 @@
     <x:numFmt numFmtId="204" formatCode="#,##0"/>
     <x:numFmt numFmtId="205" formatCode="#,##0.000000"/>
     <x:numFmt numFmtId="206" formatCode="0.0000%"/>
+    <x:numFmt numFmtId="207" formatCode=";;;"/>
   </x:numFmts>
   <x:fonts count="12">
     <x:font>
@@ -156,7 +157,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="90">
+  <x:cellXfs count="91">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -417,6 +418,9 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="205" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -1025,7 +1029,7 @@
         <v>建议 Quote 资金</v>
       </c>
       <c r="D18" s="53">
-        <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
+        <f>IF(AND(LEFT($D$51,2)="可达",ISNUMBER($D$22),ISNUMBER($D$23),ISNUMBER($D$25),ISNUMBER($D$26)),SUM($D$22:$D$23,$D$25:$D$26),"")</f>
       </c>
       <c r="E18" s="48">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
@@ -1144,13 +1148,9 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="C24" s="3" t="str">
-        <v>洗筹损耗</v>
-      </c>
-      <c r="D24" s="65">
-        <f>IF($D$51="可达",$J$52*$D$29,"")</f>
-      </c>
+    <row r="24" customHeight="1" hidden="1">
+      <c r="C24" s="3"/>
+      <c r="D24" s="90"/>
       <c r="E24" s="3">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$23,3,FALSE)</f>
       </c>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="41" t="str">
-        <v>外盘一卖一买使用卖出所得 Quote 回买；洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote。洗筹损耗另列；未模拟成交量、滑点与价格冲击。</v>
+        <v>外盘一卖一买使用卖出所得 Quote 回买；手续费仅降低洗后持币，不另列资金。洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote；未模拟成交量、滑点与价格冲击。</v>
       </c>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
@@ -4766,7 +4766,7 @@
         <v>洗筹与补回口径</v>
       </c>
       <c r="D11" s="12" t="str">
-        <v>外盘一卖一买用卖出所得 Quote 回买；洗后持币按双边费率估算，再按外盘曲线和买入费预留恢复目标所需 Quote。洗筹损耗另列。</v>
+        <v>外盘一卖一买用卖出所得 Quote 回买；双边费用仅降低洗后持币，不另列资金；只按外盘曲线和买入费预留恢复目标所需 Quote。</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999812</v>
+        <v>0.999826</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>118.59229535152608</v>
+        <v>115.03001522264874</v>
       </c>
       <c r="I14" s="20">
-        <v>118.59229535152608</v>
+        <v>115.03001522264874</v>
       </c>
       <c r="J14" s="23">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0001880353506458</v>
+        <v>1.000174030281269</v>
       </c>
       <c r="I15" s="21">
-        <v>118.59229535152608</v>
+        <v>115.03001522264874</v>
       </c>
       <c r="J15" s="24">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0001880353506458</v>
+        <v>1.000174030281269</v>
       </c>
       <c r="I16" s="21">
-        <v>791.2687585266029</v>
+        <v>772.7044505744</v>
       </c>
       <c r="J16" s="24">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>791.2687585266029</v>
+        <v>772.7044505744</v>
       </c>
       <c r="I17" s="21">
-        <v>791.2687585266029</v>
+        <v>772.7044505744</v>
       </c>
       <c r="J17" s="24">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7298112045064472</v>
+        <v>0.7068980002520439</v>
       </c>
       <c r="I18" s="21">
-        <v>791.2687585266029</v>
+        <v>772.7044505744</v>
       </c>
       <c r="J18" s="24">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>97.28829019855732</v>
+        <v>92.90616567282707</v>
       </c>
       <c r="I19" s="21">
-        <v>97.28829019855732</v>
+        <v>92.90616567282707</v>
       </c>
       <c r="J19" s="24">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>791.2687585266029</v>
+        <v>772.7044505744</v>
       </c>
       <c r="I20" s="21">
-        <v>791.2687585266029</v>
+        <v>772.7044505744</v>
       </c>
       <c r="J20" s="24">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0001880353506458</v>
+        <v>1.000174030281269</v>
       </c>
       <c r="I21" s="21">
-        <v>791.2687585266029</v>
+        <v>772.7044505744</v>
       </c>
       <c r="J21" s="24">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2758.198541325769</v>
+        <v>2686.1873966070093</v>
       </c>
       <c r="I22" s="22">
-        <v>2758.198541325769</v>
+        <v>2686.1873966070093</v>
       </c>
       <c r="J22" s="25">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0001880353506458</v>
+        <v>1.000174030281269</v>
       </c>
       <c r="I23">
-        <v>2758.198541325769</v>
+        <v>2686.1873966070093</v>
       </c>
       <c r="J23">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999826</v>
+        <v>0.999818</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>115.03001522264874</v>
+        <v>116.21115042937815</v>
       </c>
       <c r="I14" s="20">
-        <v>115.03001522264874</v>
+        <v>116.21115042937815</v>
       </c>
       <c r="J14" s="23">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.000174030281269</v>
+        <v>1.0001820331300297</v>
       </c>
       <c r="I15" s="21">
-        <v>115.03001522264874</v>
+        <v>116.21115042937815</v>
       </c>
       <c r="J15" s="24">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.000174030281269</v>
+        <v>1.0001820331300297</v>
       </c>
       <c r="I16" s="21">
-        <v>772.7044505744</v>
+        <v>774.2109063849621</v>
       </c>
       <c r="J16" s="24">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>772.7044505744</v>
+        <v>774.2109063849621</v>
       </c>
       <c r="I17" s="21">
-        <v>772.7044505744</v>
+        <v>774.2109063849621</v>
       </c>
       <c r="J17" s="24">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7068980002520439</v>
+        <v>0.7105653228887657</v>
       </c>
       <c r="I18" s="21">
-        <v>772.7044505744</v>
+        <v>774.2109063849621</v>
       </c>
       <c r="J18" s="24">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>92.90616567282707</v>
+        <v>91.94673430564363</v>
       </c>
       <c r="I19" s="21">
-        <v>92.90616567282707</v>
+        <v>91.94673430564363</v>
       </c>
       <c r="J19" s="24">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>772.7044505744</v>
+        <v>774.2109063849621</v>
       </c>
       <c r="I20" s="21">
-        <v>772.7044505744</v>
+        <v>774.2109063849621</v>
       </c>
       <c r="J20" s="24">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.000174030281269</v>
+        <v>1.0001820331300297</v>
       </c>
       <c r="I21" s="21">
-        <v>772.7044505744</v>
+        <v>774.2109063849621</v>
       </c>
       <c r="J21" s="24">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2686.1873966070093</v>
+        <v>2673.706614603858</v>
       </c>
       <c r="I22" s="22">
-        <v>2686.1873966070093</v>
+        <v>2673.706614603858</v>
       </c>
       <c r="J22" s="25">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.000174030281269</v>
+        <v>1.0001820331300297</v>
       </c>
       <c r="I23">
-        <v>2686.1873966070093</v>
+        <v>2673.706614603858</v>
       </c>
       <c r="J23">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999818</v>
+        <v>0.999822</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>116.21115042937815</v>
+        <v>120.36142433353137</v>
       </c>
       <c r="I14" s="20">
-        <v>116.21115042937815</v>
+        <v>120.36142433353137</v>
       </c>
       <c r="J14" s="23">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0001820331300297</v>
+        <v>1.0001780316896407</v>
       </c>
       <c r="I15" s="21">
-        <v>116.21115042937815</v>
+        <v>120.36142433353137</v>
       </c>
       <c r="J15" s="24">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0001820331300297</v>
+        <v>1.0001780316896407</v>
       </c>
       <c r="I16" s="21">
-        <v>774.2109063849621</v>
+        <v>772.4474956542264</v>
       </c>
       <c r="J16" s="24">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>774.2109063849621</v>
+        <v>772.4474956542264</v>
       </c>
       <c r="I17" s="21">
-        <v>774.2109063849621</v>
+        <v>772.4474956542264</v>
       </c>
       <c r="J17" s="24">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7105653228887657</v>
+        <v>0.7276395198345306</v>
       </c>
       <c r="I18" s="21">
-        <v>774.2109063849621</v>
+        <v>772.4474956542264</v>
       </c>
       <c r="J18" s="24">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>91.94673430564363</v>
+        <v>91.5963041421373</v>
       </c>
       <c r="I19" s="21">
-        <v>91.94673430564363</v>
+        <v>91.5963041421373</v>
       </c>
       <c r="J19" s="24">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>774.2109063849621</v>
+        <v>772.4474956542264</v>
       </c>
       <c r="I20" s="21">
-        <v>774.2109063849621</v>
+        <v>772.4474956542264</v>
       </c>
       <c r="J20" s="24">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0001820331300297</v>
+        <v>1.0001780316896407</v>
       </c>
       <c r="I21" s="21">
-        <v>774.2109063849621</v>
+        <v>772.4474956542264</v>
       </c>
       <c r="J21" s="24">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2673.706614603858</v>
+        <v>2685.5680311095375</v>
       </c>
       <c r="I22" s="22">
-        <v>2673.706614603858</v>
+        <v>2685.5680311095375</v>
       </c>
       <c r="J22" s="25">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0001820331300297</v>
+        <v>1.0001780316896407</v>
       </c>
       <c r="I23">
-        <v>2673.706614603858</v>
+        <v>2685.5680311095375</v>
       </c>
       <c r="J23">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999822</v>
+        <v>0.999745</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>120.36142433353137</v>
+        <v>121.33093938954433</v>
       </c>
       <c r="I14" s="20">
-        <v>120.36142433353137</v>
+        <v>121.33093938954433</v>
       </c>
       <c r="J14" s="23">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0001780316896407</v>
+        <v>1.0002550650415856</v>
       </c>
       <c r="I15" s="21">
-        <v>120.36142433353137</v>
+        <v>121.33093938954433</v>
       </c>
       <c r="J15" s="24">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0001780316896407</v>
+        <v>1.0002550650415856</v>
       </c>
       <c r="I16" s="21">
-        <v>772.4474956542264</v>
+        <v>774.4374815577972</v>
       </c>
       <c r="J16" s="24">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>772.4474956542264</v>
+        <v>774.4374815577972</v>
       </c>
       <c r="I17" s="21">
-        <v>772.4474956542264</v>
+        <v>774.4374815577972</v>
       </c>
       <c r="J17" s="24">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7276395198345306</v>
+        <v>0.7337831146942471</v>
       </c>
       <c r="I18" s="21">
-        <v>772.4474956542264</v>
+        <v>774.4374815577972</v>
       </c>
       <c r="J18" s="24">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>91.5963041421373</v>
+        <v>92.79366238390789</v>
       </c>
       <c r="I19" s="21">
-        <v>91.5963041421373</v>
+        <v>92.79366238390789</v>
       </c>
       <c r="J19" s="24">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>772.4474956542264</v>
+        <v>774.4374815577972</v>
       </c>
       <c r="I20" s="21">
-        <v>772.4474956542264</v>
+        <v>774.4374815577972</v>
       </c>
       <c r="J20" s="24">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0001780316896407</v>
+        <v>1.0002550650415856</v>
       </c>
       <c r="I21" s="21">
-        <v>772.4474956542264</v>
+        <v>774.4374815577972</v>
       </c>
       <c r="J21" s="24">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2685.5680311095375</v>
+        <v>2707.200336085702</v>
       </c>
       <c r="I22" s="22">
-        <v>2685.5680311095375</v>
+        <v>2707.200336085702</v>
       </c>
       <c r="J22" s="25">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0001780316896407</v>
+        <v>1.0002550650415856</v>
       </c>
       <c r="I23">
-        <v>2685.5680311095375</v>
+        <v>2707.200336085702</v>
       </c>
       <c r="J23">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999745</v>
+        <v>0.999689</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>121.33093938954433</v>
+        <v>118.70691785145179</v>
       </c>
       <c r="I14" s="20">
-        <v>121.33093938954433</v>
+        <v>118.70691785145179</v>
       </c>
       <c r="J14" s="23">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0002550650415856</v>
+        <v>1.0003110967510895</v>
       </c>
       <c r="I15" s="21">
-        <v>121.33093938954433</v>
+        <v>118.70691785145179</v>
       </c>
       <c r="J15" s="24">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0002550650415856</v>
+        <v>1.0003110967510895</v>
       </c>
       <c r="I16" s="21">
-        <v>774.4374815577972</v>
+        <v>763.5174539281716</v>
       </c>
       <c r="J16" s="24">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>774.4374815577972</v>
+        <v>763.5174539281716</v>
       </c>
       <c r="I17" s="21">
-        <v>774.4374815577972</v>
+        <v>763.5174539281716</v>
       </c>
       <c r="J17" s="24">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7337831146942471</v>
+        <v>0.7075230396653359</v>
       </c>
       <c r="I18" s="21">
-        <v>774.4374815577972</v>
+        <v>763.5174539281716</v>
       </c>
       <c r="J18" s="24">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>92.79366238390789</v>
+        <v>89.16773116439212</v>
       </c>
       <c r="I19" s="21">
-        <v>92.79366238390789</v>
+        <v>89.16773116439212</v>
       </c>
       <c r="J19" s="24">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>774.4374815577972</v>
+        <v>763.5174539281716</v>
       </c>
       <c r="I20" s="21">
-        <v>774.4374815577972</v>
+        <v>763.5174539281716</v>
       </c>
       <c r="J20" s="24">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0002550650415856</v>
+        <v>1.0003110967510895</v>
       </c>
       <c r="I21" s="21">
-        <v>774.4374815577972</v>
+        <v>763.5174539281716</v>
       </c>
       <c r="J21" s="24">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2707.200336085702</v>
+        <v>2649.7340672949285</v>
       </c>
       <c r="I22" s="22">
-        <v>2707.200336085702</v>
+        <v>2649.7340672949285</v>
       </c>
       <c r="J22" s="25">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0002550650415856</v>
+        <v>1.0003110967510895</v>
       </c>
       <c r="I23">
-        <v>2707.200336085702</v>
+        <v>2649.7340672949285</v>
       </c>
       <c r="J23">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999689</v>
+        <v>0.999661</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>118.70691785145179</v>
+        <v>118.33011390861502</v>
       </c>
       <c r="I14" s="20">
-        <v>118.70691785145179</v>
+        <v>118.33011390861502</v>
       </c>
       <c r="J14" s="23">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0003110967510895</v>
+        <v>1.0003391149599714</v>
       </c>
       <c r="I15" s="21">
-        <v>118.70691785145179</v>
+        <v>118.33011390861502</v>
       </c>
       <c r="J15" s="24">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0003110967510895</v>
+        <v>1.0003391149599714</v>
       </c>
       <c r="I16" s="21">
-        <v>763.5174539281716</v>
+        <v>757.7268694087296</v>
       </c>
       <c r="J16" s="24">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>763.5174539281716</v>
+        <v>757.7268694087296</v>
       </c>
       <c r="I17" s="21">
-        <v>763.5174539281716</v>
+        <v>757.7268694087296</v>
       </c>
       <c r="J17" s="24">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7075230396653359</v>
+        <v>0.7473013351526168</v>
       </c>
       <c r="I18" s="21">
-        <v>763.5174539281716</v>
+        <v>757.7268694087296</v>
       </c>
       <c r="J18" s="24">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>89.16773116439212</v>
+        <v>85.40895363528236</v>
       </c>
       <c r="I19" s="21">
-        <v>89.16773116439212</v>
+        <v>85.40895363528236</v>
       </c>
       <c r="J19" s="24">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>763.5174539281716</v>
+        <v>757.7268694087296</v>
       </c>
       <c r="I20" s="21">
-        <v>763.5174539281716</v>
+        <v>757.7268694087296</v>
       </c>
       <c r="J20" s="24">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0003110967510895</v>
+        <v>1.0003391149599714</v>
       </c>
       <c r="I21" s="21">
-        <v>763.5174539281716</v>
+        <v>757.7268694087296</v>
       </c>
       <c r="J21" s="24">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2649.7340672949285</v>
+        <v>2664.683327648073</v>
       </c>
       <c r="I22" s="22">
-        <v>2649.7340672949285</v>
+        <v>2664.683327648073</v>
       </c>
       <c r="J22" s="25">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0003110967510895</v>
+        <v>1.0003391149599714</v>
       </c>
       <c r="I23">
-        <v>2649.7340672949285</v>
+        <v>2664.683327648073</v>
       </c>
       <c r="J23">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999661</v>
+        <v>0.999656</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>118.33011390861502</v>
+        <v>118.13063693910706</v>
       </c>
       <c r="I14" s="20">
-        <v>118.33011390861502</v>
+        <v>118.13063693910706</v>
       </c>
       <c r="J14" s="23">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0003391149599714</v>
+        <v>1.0003441183767217</v>
       </c>
       <c r="I15" s="21">
-        <v>118.33011390861502</v>
+        <v>118.13063693910706</v>
       </c>
       <c r="J15" s="24">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0003391149599714</v>
+        <v>1.0003441183767217</v>
       </c>
       <c r="I16" s="21">
-        <v>757.7268694087296</v>
+        <v>766.6137151180006</v>
       </c>
       <c r="J16" s="24">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>757.7268694087296</v>
+        <v>766.6137151180006</v>
       </c>
       <c r="I17" s="21">
-        <v>757.7268694087296</v>
+        <v>766.6137151180006</v>
       </c>
       <c r="J17" s="24">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7473013351526168</v>
+        <v>0.7592481813743928</v>
       </c>
       <c r="I18" s="21">
-        <v>757.7268694087296</v>
+        <v>766.6137151180006</v>
       </c>
       <c r="J18" s="24">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>85.40895363528236</v>
+        <v>89.02062309434444</v>
       </c>
       <c r="I19" s="21">
-        <v>85.40895363528236</v>
+        <v>89.02062309434444</v>
       </c>
       <c r="J19" s="24">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>757.7268694087296</v>
+        <v>766.6137151180006</v>
       </c>
       <c r="I20" s="21">
-        <v>757.7268694087296</v>
+        <v>766.6137151180006</v>
       </c>
       <c r="J20" s="24">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0003391149599714</v>
+        <v>1.0003441183767217</v>
       </c>
       <c r="I21" s="21">
-        <v>757.7268694087296</v>
+        <v>766.6137151180006</v>
       </c>
       <c r="J21" s="24">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2664.683327648073</v>
+        <v>2693.7966660531224</v>
       </c>
       <c r="I22" s="22">
-        <v>2664.683327648073</v>
+        <v>2693.7966660531224</v>
       </c>
       <c r="J22" s="25">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0003391149599714</v>
+        <v>1.0003441183767217</v>
       </c>
       <c r="I23">
-        <v>2664.683327648073</v>
+        <v>2693.7966660531224</v>
       </c>
       <c r="J23">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999656</v>
+        <v>0.999697</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>118.13063693910706</v>
+        <v>121.58684081276627</v>
       </c>
       <c r="I14" s="20">
-        <v>118.13063693910706</v>
+        <v>121.58684081276627</v>
       </c>
       <c r="J14" s="23">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0003441183767217</v>
+        <v>1.0003030918368265</v>
       </c>
       <c r="I15" s="21">
-        <v>118.13063693910706</v>
+        <v>121.58684081276627</v>
       </c>
       <c r="J15" s="24">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0003441183767217</v>
+        <v>1.0003030918368265</v>
       </c>
       <c r="I16" s="21">
-        <v>766.6137151180006</v>
+        <v>777.3055235736429</v>
       </c>
       <c r="J16" s="24">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>766.6137151180006</v>
+        <v>777.3055235736429</v>
       </c>
       <c r="I17" s="21">
-        <v>766.6137151180006</v>
+        <v>777.3055235736429</v>
       </c>
       <c r="J17" s="24">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7592481813743928</v>
+        <v>0.7513126477322629</v>
       </c>
       <c r="I18" s="21">
-        <v>766.6137151180006</v>
+        <v>777.3055235736429</v>
       </c>
       <c r="J18" s="24">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>89.02062309434444</v>
+        <v>90.12730857449807</v>
       </c>
       <c r="I19" s="21">
-        <v>89.02062309434444</v>
+        <v>90.12730857449807</v>
       </c>
       <c r="J19" s="24">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>766.6137151180006</v>
+        <v>777.3055235736429</v>
       </c>
       <c r="I20" s="21">
-        <v>766.6137151180006</v>
+        <v>777.3055235736429</v>
       </c>
       <c r="J20" s="24">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0003441183767217</v>
+        <v>1.0003030918368265</v>
       </c>
       <c r="I21" s="21">
-        <v>766.6137151180006</v>
+        <v>777.3055235736429</v>
       </c>
       <c r="J21" s="24">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2693.7966660531224</v>
+        <v>2729.5370497260674</v>
       </c>
       <c r="I22" s="22">
-        <v>2693.7966660531224</v>
+        <v>2729.5370497260674</v>
       </c>
       <c r="J22" s="25">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0003441183767217</v>
+        <v>1.0003030918368265</v>
       </c>
       <c r="I23">
-        <v>2693.7966660531224</v>
+        <v>2729.5370497260674</v>
       </c>
       <c r="J23">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999697</v>
+        <v>0.999887</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="E8" s="5"/>
@@ -4972,17 +4972,17 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>121.58684081276627</v>
+        <v>119.6235174574727</v>
       </c>
       <c r="I14" s="20">
-        <v>121.58684081276627</v>
+        <v>119.6235174574727</v>
       </c>
       <c r="J14" s="23">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L14" s="26" t="str">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="AF14" s="35" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG14" s="35" t="inlineStr">
@@ -5088,17 +5088,17 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0003030918368265</v>
+        <v>1.0001130127704432</v>
       </c>
       <c r="I15" s="21">
-        <v>121.58684081276627</v>
+        <v>119.6235174574727</v>
       </c>
       <c r="J15" s="24">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L15" s="27" t="str">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="AF15" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG15" s="36" t="inlineStr">
@@ -5204,17 +5204,17 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0003030918368265</v>
+        <v>1.0001130127704432</v>
       </c>
       <c r="I16" s="21">
-        <v>777.3055235736429</v>
+        <v>766.2865903847136</v>
       </c>
       <c r="J16" s="24">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L16" s="27" t="str">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AF16" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG16" s="36" t="inlineStr">
@@ -5320,17 +5320,17 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>777.3055235736429</v>
+        <v>766.2865903847136</v>
       </c>
       <c r="I17" s="21">
-        <v>777.3055235736429</v>
+        <v>766.2865903847136</v>
       </c>
       <c r="J17" s="24">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L17" s="27" t="str">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="AF17" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG17" s="36" t="inlineStr">
@@ -5436,17 +5436,17 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7513126477322629</v>
+        <v>0.7096141864030636</v>
       </c>
       <c r="I18" s="21">
-        <v>777.3055235736429</v>
+        <v>766.2865903847136</v>
       </c>
       <c r="J18" s="24">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L18" s="27" t="str">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="AF18" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG18" s="36" t="inlineStr">
@@ -5552,17 +5552,17 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>90.12730857449807</v>
+        <v>88.29997789750243</v>
       </c>
       <c r="I19" s="21">
-        <v>90.12730857449807</v>
+        <v>88.29997789750243</v>
       </c>
       <c r="J19" s="24">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L19" s="27" t="str">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="AF19" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG19" s="36" t="inlineStr">
@@ -5668,17 +5668,17 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>777.3055235736429</v>
+        <v>766.2865903847136</v>
       </c>
       <c r="I20" s="21">
-        <v>777.3055235736429</v>
+        <v>766.2865903847136</v>
       </c>
       <c r="J20" s="24">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L20" s="27" t="str">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="AF20" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG20" s="36" t="inlineStr">
@@ -5784,17 +5784,17 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0003030918368265</v>
+        <v>1.0001130127704432</v>
       </c>
       <c r="I21" s="21">
-        <v>777.3055235736429</v>
+        <v>766.2865903847136</v>
       </c>
       <c r="J21" s="24">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L21" s="27" t="str">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AF21" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG21" s="36" t="inlineStr">
@@ -5900,17 +5900,17 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2729.5370497260674</v>
+        <v>2679.2227521709956</v>
       </c>
       <c r="I22" s="22">
-        <v>2729.5370497260674</v>
+        <v>2679.2227521709956</v>
       </c>
       <c r="J22" s="25">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L22" s="28" t="str">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AF22" s="37" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG22" s="37" t="inlineStr">
@@ -6016,17 +6016,17 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0003030918368265</v>
+        <v>1.0001130127704432</v>
       </c>
       <c r="I23">
-        <v>2729.5370497260674</v>
+        <v>2679.2227521709956</v>
       </c>
       <c r="J23">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L23" t="str">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999887</v>
+        <v>0.999917</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>119.6235174574727</v>
+        <v>121.0200446637071</v>
       </c>
       <c r="I14" s="20">
-        <v>119.6235174574727</v>
+        <v>121.0200446637071</v>
       </c>
       <c r="J14" s="23">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0001130127704432</v>
+        <v>1.0000830068895719</v>
       </c>
       <c r="I15" s="21">
-        <v>119.6235174574727</v>
+        <v>121.0200446637071</v>
       </c>
       <c r="J15" s="24">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0001130127704432</v>
+        <v>1.0000830068895719</v>
       </c>
       <c r="I16" s="21">
-        <v>766.2865903847136</v>
+        <v>787.8753936576736</v>
       </c>
       <c r="J16" s="24">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>766.2865903847136</v>
+        <v>787.8753936576736</v>
       </c>
       <c r="I17" s="21">
-        <v>766.2865903847136</v>
+        <v>787.8753936576736</v>
       </c>
       <c r="J17" s="24">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7096141864030636</v>
+        <v>0.7174125452412551</v>
       </c>
       <c r="I18" s="21">
-        <v>766.2865903847136</v>
+        <v>787.8753936576736</v>
       </c>
       <c r="J18" s="24">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>88.29997789750243</v>
+        <v>89.76745069840798</v>
       </c>
       <c r="I19" s="21">
-        <v>88.29997789750243</v>
+        <v>89.76745069840798</v>
       </c>
       <c r="J19" s="24">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>766.2865903847136</v>
+        <v>787.8753936576736</v>
       </c>
       <c r="I20" s="21">
-        <v>766.2865903847136</v>
+        <v>787.8753936576736</v>
       </c>
       <c r="J20" s="24">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0001130127704432</v>
+        <v>1.0000830068895719</v>
       </c>
       <c r="I21" s="21">
-        <v>766.2865903847136</v>
+        <v>787.8753936576736</v>
       </c>
       <c r="J21" s="24">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2679.2227521709956</v>
+        <v>2695.7437467309787</v>
       </c>
       <c r="I22" s="22">
-        <v>2679.2227521709956</v>
+        <v>2695.7437467309787</v>
       </c>
       <c r="J22" s="25">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0001130127704432</v>
+        <v>1.0000830068895719</v>
       </c>
       <c r="I23">
-        <v>2679.2227521709956</v>
+        <v>2695.7437467309787</v>
       </c>
       <c r="J23">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999917</v>
+        <v>0.999727</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>121.0200446637071</v>
+        <v>121.59319494221923</v>
       </c>
       <c r="I14" s="20">
-        <v>121.0200446637071</v>
+        <v>121.59319494221923</v>
       </c>
       <c r="J14" s="23">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0000830068895719</v>
+        <v>1.000273074549352</v>
       </c>
       <c r="I15" s="21">
-        <v>121.0200446637071</v>
+        <v>121.59319494221923</v>
       </c>
       <c r="J15" s="24">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0000830068895719</v>
+        <v>1.000273074549352</v>
       </c>
       <c r="I16" s="21">
-        <v>787.8753936576736</v>
+        <v>794.5869222297687</v>
       </c>
       <c r="J16" s="24">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>787.8753936576736</v>
+        <v>794.5869222297687</v>
       </c>
       <c r="I17" s="21">
-        <v>787.8753936576736</v>
+        <v>794.5869222297687</v>
       </c>
       <c r="J17" s="24">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7174125452412551</v>
+        <v>0.7251289602061363</v>
       </c>
       <c r="I18" s="21">
-        <v>787.8753936576736</v>
+        <v>794.5869222297687</v>
       </c>
       <c r="J18" s="24">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>89.76745069840798</v>
+        <v>92.06513378152236</v>
       </c>
       <c r="I19" s="21">
-        <v>89.76745069840798</v>
+        <v>92.06513378152236</v>
       </c>
       <c r="J19" s="24">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>787.8753936576736</v>
+        <v>794.5869222297687</v>
       </c>
       <c r="I20" s="21">
-        <v>787.8753936576736</v>
+        <v>794.5869222297687</v>
       </c>
       <c r="J20" s="24">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0000830068895719</v>
+        <v>1.000273074549352</v>
       </c>
       <c r="I21" s="21">
-        <v>787.8753936576736</v>
+        <v>794.5869222297687</v>
       </c>
       <c r="J21" s="24">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2695.7437467309787</v>
+        <v>2727.264543220299</v>
       </c>
       <c r="I22" s="22">
-        <v>2695.7437467309787</v>
+        <v>2727.264543220299</v>
       </c>
       <c r="J22" s="25">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0000830068895719</v>
+        <v>1.000273074549352</v>
       </c>
       <c r="I23">
-        <v>2695.7437467309787</v>
+        <v>2727.264543220299</v>
       </c>
       <c r="J23">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999727</v>
+        <v>0.999819</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>121.59319494221923</v>
+        <v>120.12174203530839</v>
       </c>
       <c r="I14" s="20">
-        <v>121.59319494221923</v>
+        <v>120.12174203530839</v>
       </c>
       <c r="J14" s="23">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.000273074549352</v>
+        <v>1.0001810327669307</v>
       </c>
       <c r="I15" s="21">
-        <v>121.59319494221923</v>
+        <v>120.12174203530839</v>
       </c>
       <c r="J15" s="24">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.000273074549352</v>
+        <v>1.0001810327669307</v>
       </c>
       <c r="I16" s="21">
-        <v>794.5869222297687</v>
+        <v>779.7911421967376</v>
       </c>
       <c r="J16" s="24">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>794.5869222297687</v>
+        <v>779.7911421967376</v>
       </c>
       <c r="I17" s="21">
-        <v>794.5869222297687</v>
+        <v>779.7911421967376</v>
       </c>
       <c r="J17" s="24">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7251289602061363</v>
+        <v>0.7354101092297706</v>
       </c>
       <c r="I18" s="21">
-        <v>794.5869222297687</v>
+        <v>779.7911421967376</v>
       </c>
       <c r="J18" s="24">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>92.06513378152236</v>
+        <v>92.92681975437554</v>
       </c>
       <c r="I19" s="21">
-        <v>92.06513378152236</v>
+        <v>92.92681975437554</v>
       </c>
       <c r="J19" s="24">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>794.5869222297687</v>
+        <v>779.7911421967376</v>
       </c>
       <c r="I20" s="21">
-        <v>794.5869222297687</v>
+        <v>779.7911421967376</v>
       </c>
       <c r="J20" s="24">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.000273074549352</v>
+        <v>1.0001810327669307</v>
       </c>
       <c r="I21" s="21">
-        <v>794.5869222297687</v>
+        <v>779.7911421967376</v>
       </c>
       <c r="J21" s="24">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2727.264543220299</v>
+        <v>2704.849577773577</v>
       </c>
       <c r="I22" s="22">
-        <v>2727.264543220299</v>
+        <v>2704.849577773577</v>
       </c>
       <c r="J22" s="25">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.000273074549352</v>
+        <v>1.0001810327669307</v>
       </c>
       <c r="I23">
-        <v>2727.264543220299</v>
+        <v>2704.849577773577</v>
       </c>
       <c r="J23">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4637,7 +4637,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="E8" s="5"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L14" s="26" t="str">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="AF14" s="35" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG14" s="35" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L15" s="27" t="str">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="AF15" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG15" s="36" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L16" s="27" t="str">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AF16" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG16" s="36" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L17" s="27" t="str">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="AF17" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG17" s="36" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L18" s="27" t="str">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="AF18" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG18" s="36" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L19" s="27" t="str">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="AF19" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG19" s="36" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L20" s="27" t="str">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="AF20" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG20" s="36" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L21" s="27" t="str">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AF21" s="36" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG21" s="36" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L22" s="28" t="str">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AF22" s="37" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG22" s="37" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="L23" t="str">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999819</v>
+        <v>0.999865</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>120.12174203530839</v>
+        <v>118.83604286578688</v>
       </c>
       <c r="I14" s="20">
-        <v>120.12174203530839</v>
+        <v>118.83604286578688</v>
       </c>
       <c r="J14" s="23">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0001810327669307</v>
+        <v>1.0001350182274606</v>
       </c>
       <c r="I15" s="21">
-        <v>120.12174203530839</v>
+        <v>118.83604286578688</v>
       </c>
       <c r="J15" s="24">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0001810327669307</v>
+        <v>1.0001350182274606</v>
       </c>
       <c r="I16" s="21">
-        <v>779.7911421967376</v>
+        <v>768.7737844609022</v>
       </c>
       <c r="J16" s="24">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>779.7911421967376</v>
+        <v>768.7737844609022</v>
       </c>
       <c r="I17" s="21">
-        <v>779.7911421967376</v>
+        <v>768.7737844609022</v>
       </c>
       <c r="J17" s="24">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7354101092297706</v>
+        <v>0.7130532621903957</v>
       </c>
       <c r="I18" s="21">
-        <v>779.7911421967376</v>
+        <v>768.7737844609022</v>
       </c>
       <c r="J18" s="24">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>92.92681975437554</v>
+        <v>91.16230691143305</v>
       </c>
       <c r="I19" s="21">
-        <v>92.92681975437554</v>
+        <v>91.16230691143305</v>
       </c>
       <c r="J19" s="24">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>779.7911421967376</v>
+        <v>768.7737844609022</v>
       </c>
       <c r="I20" s="21">
-        <v>779.7911421967376</v>
+        <v>768.7737844609022</v>
       </c>
       <c r="J20" s="24">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0001810327669307</v>
+        <v>1.0001350182274606</v>
       </c>
       <c r="I21" s="21">
-        <v>779.7911421967376</v>
+        <v>768.7737844609022</v>
       </c>
       <c r="J21" s="24">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2704.849577773577</v>
+        <v>2617.743395358373</v>
       </c>
       <c r="I22" s="22">
-        <v>2704.849577773577</v>
+        <v>2617.743395358373</v>
       </c>
       <c r="J22" s="25">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0001810327669307</v>
+        <v>1.0001350182274606</v>
       </c>
       <c r="I23">
-        <v>2704.849577773577</v>
+        <v>2617.743395358373</v>
       </c>
       <c r="J23">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999865</v>
+        <v>0.999439</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>118.83604286578688</v>
+        <v>115.6748936153182</v>
       </c>
       <c r="I14" s="20">
-        <v>118.83604286578688</v>
+        <v>115.6748936153182</v>
       </c>
       <c r="J14" s="23">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0001350182274606</v>
+        <v>1.0005613148976575</v>
       </c>
       <c r="I15" s="21">
-        <v>118.83604286578688</v>
+        <v>115.6748936153182</v>
       </c>
       <c r="J15" s="24">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0001350182274606</v>
+        <v>1.0005613148976575</v>
       </c>
       <c r="I16" s="21">
-        <v>768.7737844609022</v>
+        <v>770.5522798289841</v>
       </c>
       <c r="J16" s="24">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>768.7737844609022</v>
+        <v>770.5522798289841</v>
       </c>
       <c r="I17" s="21">
-        <v>768.7737844609022</v>
+        <v>770.5522798289841</v>
       </c>
       <c r="J17" s="24">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7130532621903957</v>
+        <v>0.715930637087406</v>
       </c>
       <c r="I18" s="21">
-        <v>768.7737844609022</v>
+        <v>770.5522798289841</v>
       </c>
       <c r="J18" s="24">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>91.16230691143305</v>
+        <v>87.6091487324389</v>
       </c>
       <c r="I19" s="21">
-        <v>91.16230691143305</v>
+        <v>87.6091487324389</v>
       </c>
       <c r="J19" s="24">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>768.7737844609022</v>
+        <v>770.5522798289841</v>
       </c>
       <c r="I20" s="21">
-        <v>768.7737844609022</v>
+        <v>770.5522798289841</v>
       </c>
       <c r="J20" s="24">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0001350182274606</v>
+        <v>1.0005613148976575</v>
       </c>
       <c r="I21" s="21">
-        <v>768.7737844609022</v>
+        <v>770.5522798289841</v>
       </c>
       <c r="J21" s="24">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2617.743395358373</v>
+        <v>2573.9239713479265</v>
       </c>
       <c r="I22" s="22">
-        <v>2617.743395358373</v>
+        <v>2573.9239713479265</v>
       </c>
       <c r="J22" s="25">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0001350182274606</v>
+        <v>1.0005613148976575</v>
       </c>
       <c r="I23">
-        <v>2617.743395358373</v>
+        <v>2573.9239713479265</v>
       </c>
       <c r="J23">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999439</v>
+        <v>0.999327</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>115.6748936153182</v>
+        <v>110.56440984782759</v>
       </c>
       <c r="I14" s="20">
-        <v>115.6748936153182</v>
+        <v>110.56440984782759</v>
       </c>
       <c r="J14" s="23">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0005613148976575</v>
+        <v>1.0006734532340265</v>
       </c>
       <c r="I15" s="21">
-        <v>115.6748936153182</v>
+        <v>110.56440984782759</v>
       </c>
       <c r="J15" s="24">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0005613148976575</v>
+        <v>1.0006734532340265</v>
       </c>
       <c r="I16" s="21">
-        <v>770.5522798289841</v>
+        <v>744.2308673737426</v>
       </c>
       <c r="J16" s="24">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>770.5522798289841</v>
+        <v>744.2308673737426</v>
       </c>
       <c r="I17" s="21">
-        <v>770.5522798289841</v>
+        <v>744.2308673737426</v>
       </c>
       <c r="J17" s="24">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.715930637087406</v>
+        <v>0.7000361243116617</v>
       </c>
       <c r="I18" s="21">
-        <v>770.5522798289841</v>
+        <v>744.2308673737426</v>
       </c>
       <c r="J18" s="24">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>87.6091487324389</v>
+        <v>85.97786310186756</v>
       </c>
       <c r="I19" s="21">
-        <v>87.6091487324389</v>
+        <v>85.97786310186756</v>
       </c>
       <c r="J19" s="24">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>770.5522798289841</v>
+        <v>744.2308673737426</v>
       </c>
       <c r="I20" s="21">
-        <v>770.5522798289841</v>
+        <v>744.2308673737426</v>
       </c>
       <c r="J20" s="24">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0005613148976575</v>
+        <v>1.0006734532340265</v>
       </c>
       <c r="I21" s="21">
-        <v>770.5522798289841</v>
+        <v>744.2308673737426</v>
       </c>
       <c r="J21" s="24">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2573.9239713479265</v>
+        <v>2502.464158378589</v>
       </c>
       <c r="I22" s="22">
-        <v>2573.9239713479265</v>
+        <v>2502.464158378589</v>
       </c>
       <c r="J22" s="25">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0005613148976575</v>
+        <v>1.0006734532340265</v>
       </c>
       <c r="I23">
-        <v>2573.9239713479265</v>
+        <v>2502.464158378589</v>
       </c>
       <c r="J23">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999327</v>
+        <v>0.999255</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>110.56440984782759</v>
+        <v>109.88186198718044</v>
       </c>
       <c r="I14" s="20">
-        <v>110.56440984782759</v>
+        <v>109.88186198718044</v>
       </c>
       <c r="J14" s="23">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0006734532340265</v>
+        <v>1.0007455554388018</v>
       </c>
       <c r="I15" s="21">
-        <v>110.56440984782759</v>
+        <v>109.88186198718044</v>
       </c>
       <c r="J15" s="24">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0006734532340265</v>
+        <v>1.0007455554388018</v>
       </c>
       <c r="I16" s="21">
-        <v>744.2308673737426</v>
+        <v>748.2074145238203</v>
       </c>
       <c r="J16" s="24">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>744.2308673737426</v>
+        <v>748.2074145238203</v>
       </c>
       <c r="I17" s="21">
-        <v>744.2308673737426</v>
+        <v>748.2074145238203</v>
       </c>
       <c r="J17" s="24">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7000361243116617</v>
+        <v>0.7112268640136902</v>
       </c>
       <c r="I18" s="21">
-        <v>744.2308673737426</v>
+        <v>748.2074145238203</v>
       </c>
       <c r="J18" s="24">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>85.97786310186756</v>
+        <v>84.362850323491</v>
       </c>
       <c r="I19" s="21">
-        <v>85.97786310186756</v>
+        <v>84.362850323491</v>
       </c>
       <c r="J19" s="24">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>744.2308673737426</v>
+        <v>748.2074145238203</v>
       </c>
       <c r="I20" s="21">
-        <v>744.2308673737426</v>
+        <v>748.2074145238203</v>
       </c>
       <c r="J20" s="24">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0006734532340265</v>
+        <v>1.0007455554388018</v>
       </c>
       <c r="I21" s="21">
-        <v>744.2308673737426</v>
+        <v>748.2074145238203</v>
       </c>
       <c r="J21" s="24">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2502.464158378589</v>
+        <v>2492.967260609154</v>
       </c>
       <c r="I22" s="22">
-        <v>2502.464158378589</v>
+        <v>2492.967260609154</v>
       </c>
       <c r="J22" s="25">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0006734532340265</v>
+        <v>1.0007455554388018</v>
       </c>
       <c r="I23">
-        <v>2502.464158378589</v>
+        <v>2492.967260609154</v>
       </c>
       <c r="J23">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999255</v>
+        <v>0.999127</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>109.88186198718044</v>
+        <v>109.4655634368804</v>
       </c>
       <c r="I14" s="20">
-        <v>109.88186198718044</v>
+        <v>109.4655634368804</v>
       </c>
       <c r="J14" s="23">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0007455554388018</v>
+        <v>1.00087376279492</v>
       </c>
       <c r="I15" s="21">
-        <v>109.88186198718044</v>
+        <v>109.4655634368804</v>
       </c>
       <c r="J15" s="24">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0007455554388018</v>
+        <v>1.00087376279492</v>
       </c>
       <c r="I16" s="21">
-        <v>748.2074145238203</v>
+        <v>747.5726309067816</v>
       </c>
       <c r="J16" s="24">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>748.2074145238203</v>
+        <v>747.5726309067816</v>
       </c>
       <c r="I17" s="21">
-        <v>748.2074145238203</v>
+        <v>747.5726309067816</v>
       </c>
       <c r="J17" s="24">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7112268640136902</v>
+        <v>0.7117943965081517</v>
       </c>
       <c r="I18" s="21">
-        <v>748.2074145238203</v>
+        <v>747.5726309067816</v>
       </c>
       <c r="J18" s="24">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>84.362850323491</v>
+        <v>84.78401644635767</v>
       </c>
       <c r="I19" s="21">
-        <v>84.362850323491</v>
+        <v>84.78401644635767</v>
       </c>
       <c r="J19" s="24">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>748.2074145238203</v>
+        <v>747.5726309067816</v>
       </c>
       <c r="I20" s="21">
-        <v>748.2074145238203</v>
+        <v>747.5726309067816</v>
       </c>
       <c r="J20" s="24">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0007455554388018</v>
+        <v>1.00087376279492</v>
       </c>
       <c r="I21" s="21">
-        <v>748.2074145238203</v>
+        <v>747.5726309067816</v>
       </c>
       <c r="J21" s="24">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2492.967260609154</v>
+        <v>2500.62304391734</v>
       </c>
       <c r="I22" s="22">
-        <v>2492.967260609154</v>
+        <v>2500.62304391734</v>
       </c>
       <c r="J22" s="25">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0007455554388018</v>
+        <v>1.00087376279492</v>
       </c>
       <c r="I23">
-        <v>2492.967260609154</v>
+        <v>2500.62304391734</v>
       </c>
       <c r="J23">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999127</v>
+        <v>0.999285</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>109.4655634368804</v>
+        <v>112.70058091535448</v>
       </c>
       <c r="I14" s="20">
-        <v>109.4655634368804</v>
+        <v>112.70058091535448</v>
       </c>
       <c r="J14" s="23">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.00087376279492</v>
+        <v>1.0007155115907875</v>
       </c>
       <c r="I15" s="21">
-        <v>109.4655634368804</v>
+        <v>112.70058091535448</v>
       </c>
       <c r="J15" s="24">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.00087376279492</v>
+        <v>1.0007155115907875</v>
       </c>
       <c r="I16" s="21">
-        <v>747.5726309067816</v>
+        <v>754.6195529803811</v>
       </c>
       <c r="J16" s="24">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>747.5726309067816</v>
+        <v>754.6195529803811</v>
       </c>
       <c r="I17" s="21">
-        <v>747.5726309067816</v>
+        <v>754.6195529803811</v>
       </c>
       <c r="J17" s="24">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7117943965081517</v>
+        <v>0.7104799931951346</v>
       </c>
       <c r="I18" s="21">
-        <v>747.5726309067816</v>
+        <v>754.6195529803811</v>
       </c>
       <c r="J18" s="24">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>84.78401644635767</v>
+        <v>87.5626072641939</v>
       </c>
       <c r="I19" s="21">
-        <v>84.78401644635767</v>
+        <v>87.5626072641939</v>
       </c>
       <c r="J19" s="24">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>747.5726309067816</v>
+        <v>754.6195529803811</v>
       </c>
       <c r="I20" s="21">
-        <v>747.5726309067816</v>
+        <v>754.6195529803811</v>
       </c>
       <c r="J20" s="24">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.00087376279492</v>
+        <v>1.0007155115907875</v>
       </c>
       <c r="I21" s="21">
-        <v>747.5726309067816</v>
+        <v>754.6195529803811</v>
       </c>
       <c r="J21" s="24">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2500.62304391734</v>
+        <v>2566.294900854111</v>
       </c>
       <c r="I22" s="22">
-        <v>2500.62304391734</v>
+        <v>2566.294900854111</v>
       </c>
       <c r="J22" s="25">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.00087376279492</v>
+        <v>1.0007155115907875</v>
       </c>
       <c r="I23">
-        <v>2500.62304391734</v>
+        <v>2566.294900854111</v>
       </c>
       <c r="J23">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999285</v>
+        <v>0.99922</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>112.70058091535448</v>
+        <v>108.81487560297032</v>
       </c>
       <c r="I14" s="20">
-        <v>112.70058091535448</v>
+        <v>108.81487560297032</v>
       </c>
       <c r="J14" s="23">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0007155115907875</v>
+        <v>1.0007806088749225</v>
       </c>
       <c r="I15" s="21">
-        <v>112.70058091535448</v>
+        <v>108.81487560297032</v>
       </c>
       <c r="J15" s="24">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0007155115907875</v>
+        <v>1.0007806088749225</v>
       </c>
       <c r="I16" s="21">
-        <v>754.6195529803811</v>
+        <v>746.3521546806509</v>
       </c>
       <c r="J16" s="24">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>754.6195529803811</v>
+        <v>746.3521546806509</v>
       </c>
       <c r="I17" s="21">
-        <v>754.6195529803811</v>
+        <v>746.3521546806509</v>
       </c>
       <c r="J17" s="24">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7104799931951346</v>
+        <v>0.7006064730489783</v>
       </c>
       <c r="I18" s="21">
-        <v>754.6195529803811</v>
+        <v>746.3521546806509</v>
       </c>
       <c r="J18" s="24">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>87.5626072641939</v>
+        <v>83.24493104621605</v>
       </c>
       <c r="I19" s="21">
-        <v>87.5626072641939</v>
+        <v>83.24493104621605</v>
       </c>
       <c r="J19" s="24">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>754.6195529803811</v>
+        <v>746.3521546806509</v>
       </c>
       <c r="I20" s="21">
-        <v>754.6195529803811</v>
+        <v>746.3521546806509</v>
       </c>
       <c r="J20" s="24">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0007155115907875</v>
+        <v>1.0007806088749225</v>
       </c>
       <c r="I21" s="21">
-        <v>754.6195529803811</v>
+        <v>746.3521546806509</v>
       </c>
       <c r="J21" s="24">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2566.294900854111</v>
+        <v>2534.8972198314686</v>
       </c>
       <c r="I22" s="22">
-        <v>2566.294900854111</v>
+        <v>2534.8972198314686</v>
       </c>
       <c r="J22" s="25">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0007155115907875</v>
+        <v>1.0007806088749225</v>
       </c>
       <c r="I23">
-        <v>2566.294900854111</v>
+        <v>2534.8972198314686</v>
       </c>
       <c r="J23">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.99922</v>
+        <v>0.999272</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>108.81487560297032</v>
+        <v>107.35815673810534</v>
       </c>
       <c r="I14" s="20">
-        <v>108.81487560297032</v>
+        <v>107.35815673810534</v>
       </c>
       <c r="J14" s="23">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0007806088749225</v>
+        <v>1.0007285303701094</v>
       </c>
       <c r="I15" s="21">
-        <v>108.81487560297032</v>
+        <v>107.35815673810534</v>
       </c>
       <c r="J15" s="24">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0007806088749225</v>
+        <v>1.0007285303701094</v>
       </c>
       <c r="I16" s="21">
-        <v>746.3521546806509</v>
+        <v>743.3311450736135</v>
       </c>
       <c r="J16" s="24">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>746.3521546806509</v>
+        <v>743.3311450736135</v>
       </c>
       <c r="I17" s="21">
-        <v>746.3521546806509</v>
+        <v>743.3311450736135</v>
       </c>
       <c r="J17" s="24">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7006064730489783</v>
+        <v>0.699956568381782</v>
       </c>
       <c r="I18" s="21">
-        <v>746.3521546806509</v>
+        <v>743.3311450736135</v>
       </c>
       <c r="J18" s="24">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>83.24493104621605</v>
+        <v>81.94965935200825</v>
       </c>
       <c r="I19" s="21">
-        <v>83.24493104621605</v>
+        <v>81.94965935200825</v>
       </c>
       <c r="J19" s="24">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>746.3521546806509</v>
+        <v>743.3311450736135</v>
       </c>
       <c r="I20" s="21">
-        <v>746.3521546806509</v>
+        <v>743.3311450736135</v>
       </c>
       <c r="J20" s="24">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0007806088749225</v>
+        <v>1.0007285303701094</v>
       </c>
       <c r="I21" s="21">
-        <v>746.3521546806509</v>
+        <v>743.3311450736135</v>
       </c>
       <c r="J21" s="24">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2534.8972198314686</v>
+        <v>2506.62482287105</v>
       </c>
       <c r="I22" s="22">
-        <v>2534.8972198314686</v>
+        <v>2506.62482287105</v>
       </c>
       <c r="J22" s="25">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0007806088749225</v>
+        <v>1.0007285303701094</v>
       </c>
       <c r="I23">
-        <v>2534.8972198314686</v>
+        <v>2506.62482287105</v>
       </c>
       <c r="J23">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999272</v>
+        <v>0.999087</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>107.35815673810534</v>
+        <v>101.63279073794375</v>
       </c>
       <c r="I14" s="20">
-        <v>107.35815673810534</v>
+        <v>101.63279073794375</v>
       </c>
       <c r="J14" s="23">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0007285303701094</v>
+        <v>1.000913834330744</v>
       </c>
       <c r="I15" s="21">
-        <v>107.35815673810534</v>
+        <v>101.63279073794375</v>
       </c>
       <c r="J15" s="24">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0007285303701094</v>
+        <v>1.000913834330744</v>
       </c>
       <c r="I16" s="21">
-        <v>743.3311450736135</v>
+        <v>713.8517466446867</v>
       </c>
       <c r="J16" s="24">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>743.3311450736135</v>
+        <v>713.8517466446867</v>
       </c>
       <c r="I17" s="21">
-        <v>743.3311450736135</v>
+        <v>713.8517466446867</v>
       </c>
       <c r="J17" s="24">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.699956568381782</v>
+        <v>0.6810788249671951</v>
       </c>
       <c r="I18" s="21">
-        <v>743.3311450736135</v>
+        <v>713.8517466446867</v>
       </c>
       <c r="J18" s="24">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>81.94965935200825</v>
+        <v>80.02306105474298</v>
       </c>
       <c r="I19" s="21">
-        <v>81.94965935200825</v>
+        <v>80.02306105474298</v>
       </c>
       <c r="J19" s="24">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>743.3311450736135</v>
+        <v>713.8517466446867</v>
       </c>
       <c r="I20" s="21">
-        <v>743.3311450736135</v>
+        <v>713.8517466446867</v>
       </c>
       <c r="J20" s="24">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0007285303701094</v>
+        <v>1.000913834330744</v>
       </c>
       <c r="I21" s="21">
-        <v>743.3311450736135</v>
+        <v>713.8517466446867</v>
       </c>
       <c r="J21" s="24">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2506.62482287105</v>
+        <v>2349.7953631665714</v>
       </c>
       <c r="I22" s="22">
-        <v>2506.62482287105</v>
+        <v>2349.7953631665714</v>
       </c>
       <c r="J22" s="25">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0007285303701094</v>
+        <v>1.000913834330744</v>
       </c>
       <c r="I23">
-        <v>2506.62482287105</v>
+        <v>2349.7953631665714</v>
       </c>
       <c r="J23">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999087</v>
+        <v>0.99913</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>101.63279073794375</v>
+        <v>105.95217839520383</v>
       </c>
       <c r="I14" s="20">
-        <v>101.63279073794375</v>
+        <v>105.95217839520383</v>
       </c>
       <c r="J14" s="23">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.000913834330744</v>
+        <v>1.0008707575590765</v>
       </c>
       <c r="I15" s="21">
-        <v>101.63279073794375</v>
+        <v>105.95217839520383</v>
       </c>
       <c r="J15" s="24">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.000913834330744</v>
+        <v>1.0008707575590765</v>
       </c>
       <c r="I16" s="21">
-        <v>713.8517466446867</v>
+        <v>730.6656791408525</v>
       </c>
       <c r="J16" s="24">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>713.8517466446867</v>
+        <v>730.6656791408525</v>
       </c>
       <c r="I17" s="21">
-        <v>713.8517466446867</v>
+        <v>730.6656791408525</v>
       </c>
       <c r="J17" s="24">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.6810788249671951</v>
+        <v>0.7107343388748211</v>
       </c>
       <c r="I18" s="21">
-        <v>713.8517466446867</v>
+        <v>730.6656791408525</v>
       </c>
       <c r="J18" s="24">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>80.02306105474298</v>
+        <v>81.00047040925607</v>
       </c>
       <c r="I19" s="21">
-        <v>80.02306105474298</v>
+        <v>81.00047040925607</v>
       </c>
       <c r="J19" s="24">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>713.8517466446867</v>
+        <v>730.6656791408525</v>
       </c>
       <c r="I20" s="21">
-        <v>713.8517466446867</v>
+        <v>730.6656791408525</v>
       </c>
       <c r="J20" s="24">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.000913834330744</v>
+        <v>1.0008707575590765</v>
       </c>
       <c r="I21" s="21">
-        <v>713.8517466446867</v>
+        <v>730.6656791408525</v>
       </c>
       <c r="J21" s="24">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2349.7953631665714</v>
+        <v>2446.998889033459</v>
       </c>
       <c r="I22" s="22">
-        <v>2349.7953631665714</v>
+        <v>2446.998889033459</v>
       </c>
       <c r="J22" s="25">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.000913834330744</v>
+        <v>1.0008707575590765</v>
       </c>
       <c r="I23">
-        <v>2349.7953631665714</v>
+        <v>2446.998889033459</v>
       </c>
       <c r="J23">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.99913</v>
+        <v>0.998953</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>105.95217839520383</v>
+        <v>104.79972531240209</v>
       </c>
       <c r="I14" s="20">
-        <v>105.95217839520383</v>
+        <v>104.79972531240209</v>
       </c>
       <c r="J14" s="23">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0008707575590765</v>
+        <v>1.0010480973579339</v>
       </c>
       <c r="I15" s="21">
-        <v>105.95217839520383</v>
+        <v>104.79972531240209</v>
       </c>
       <c r="J15" s="24">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0008707575590765</v>
+        <v>1.0010480973579339</v>
       </c>
       <c r="I16" s="21">
-        <v>730.6656791408525</v>
+        <v>722.1160555101192</v>
       </c>
       <c r="J16" s="24">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>730.6656791408525</v>
+        <v>722.1160555101192</v>
       </c>
       <c r="I17" s="21">
-        <v>730.6656791408525</v>
+        <v>722.1160555101192</v>
       </c>
       <c r="J17" s="24">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7107343388748211</v>
+        <v>0.7031942443738595</v>
       </c>
       <c r="I18" s="21">
-        <v>730.6656791408525</v>
+        <v>722.1160555101192</v>
       </c>
       <c r="J18" s="24">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>81.00047040925607</v>
+        <v>79.72347047358585</v>
       </c>
       <c r="I19" s="21">
-        <v>81.00047040925607</v>
+        <v>79.72347047358585</v>
       </c>
       <c r="J19" s="24">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>730.6656791408525</v>
+        <v>722.1160555101192</v>
       </c>
       <c r="I20" s="21">
-        <v>730.6656791408525</v>
+        <v>722.1160555101192</v>
       </c>
       <c r="J20" s="24">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0008707575590765</v>
+        <v>1.0010480973579339</v>
       </c>
       <c r="I21" s="21">
-        <v>730.6656791408525</v>
+        <v>722.1160555101192</v>
       </c>
       <c r="J21" s="24">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2446.998889033459</v>
+        <v>2427.3814683974124</v>
       </c>
       <c r="I22" s="22">
-        <v>2446.998889033459</v>
+        <v>2427.3814683974124</v>
       </c>
       <c r="J22" s="25">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0008707575590765</v>
+        <v>1.0010480973579339</v>
       </c>
       <c r="I23">
-        <v>2446.998889033459</v>
+        <v>2427.3814683974124</v>
       </c>
       <c r="J23">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.998953</v>
+        <v>0.999117</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>104.79972531240209</v>
+        <v>103.6114889447382</v>
       </c>
       <c r="I14" s="20">
-        <v>104.79972531240209</v>
+        <v>103.6114889447382</v>
       </c>
       <c r="J14" s="23">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0010480973579339</v>
+        <v>1.000883780378074</v>
       </c>
       <c r="I15" s="21">
-        <v>104.79972531240209</v>
+        <v>103.6114889447382</v>
       </c>
       <c r="J15" s="24">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0010480973579339</v>
+        <v>1.000883780378074</v>
       </c>
       <c r="I16" s="21">
-        <v>722.1160555101192</v>
+        <v>720.0357916039862</v>
       </c>
       <c r="J16" s="24">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>722.1160555101192</v>
+        <v>720.0357916039862</v>
       </c>
       <c r="I17" s="21">
-        <v>722.1160555101192</v>
+        <v>720.0357916039862</v>
       </c>
       <c r="J17" s="24">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7031942443738595</v>
+        <v>0.7078420245076402</v>
       </c>
       <c r="I18" s="21">
-        <v>722.1160555101192</v>
+        <v>720.0357916039862</v>
       </c>
       <c r="J18" s="24">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>79.72347047358585</v>
+        <v>78.48930605724856</v>
       </c>
       <c r="I19" s="21">
-        <v>79.72347047358585</v>
+        <v>78.48930605724856</v>
       </c>
       <c r="J19" s="24">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>722.1160555101192</v>
+        <v>720.0357916039862</v>
       </c>
       <c r="I20" s="21">
-        <v>722.1160555101192</v>
+        <v>720.0357916039862</v>
       </c>
       <c r="J20" s="24">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0010480973579339</v>
+        <v>1.000883780378074</v>
       </c>
       <c r="I21" s="21">
-        <v>722.1160555101192</v>
+        <v>720.0357916039862</v>
       </c>
       <c r="J21" s="24">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2427.3814683974124</v>
+        <v>2412.0898753599427</v>
       </c>
       <c r="I22" s="22">
-        <v>2427.3814683974124</v>
+        <v>2412.0898753599427</v>
       </c>
       <c r="J22" s="25">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0010480973579339</v>
+        <v>1.000883780378074</v>
       </c>
       <c r="I23">
-        <v>2427.3814683974124</v>
+        <v>2412.0898753599427</v>
       </c>
       <c r="J23">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999117</v>
+        <v>0.999339</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>103.6114889447382</v>
+        <v>105.64983454063136</v>
       </c>
       <c r="I14" s="20">
-        <v>103.6114889447382</v>
+        <v>105.64983454063136</v>
       </c>
       <c r="J14" s="23">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.000883780378074</v>
+        <v>1.0006614372099958</v>
       </c>
       <c r="I15" s="21">
-        <v>103.6114889447382</v>
+        <v>105.64983454063136</v>
       </c>
       <c r="J15" s="24">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.000883780378074</v>
+        <v>1.0006614372099958</v>
       </c>
       <c r="I16" s="21">
-        <v>720.0357916039862</v>
+        <v>726.9104878324572</v>
       </c>
       <c r="J16" s="24">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>720.0357916039862</v>
+        <v>726.9104878324572</v>
       </c>
       <c r="I17" s="21">
-        <v>720.0357916039862</v>
+        <v>726.9104878324572</v>
       </c>
       <c r="J17" s="24">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7078420245076402</v>
+        <v>0.7023422482260775</v>
       </c>
       <c r="I18" s="21">
-        <v>720.0357916039862</v>
+        <v>726.9104878324572</v>
       </c>
       <c r="J18" s="24">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>78.48930605724856</v>
+        <v>80.17299434926487</v>
       </c>
       <c r="I19" s="21">
-        <v>78.48930605724856</v>
+        <v>80.17299434926487</v>
       </c>
       <c r="J19" s="24">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>720.0357916039862</v>
+        <v>726.9104878324572</v>
       </c>
       <c r="I20" s="21">
-        <v>720.0357916039862</v>
+        <v>726.9104878324572</v>
       </c>
       <c r="J20" s="24">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.000883780378074</v>
+        <v>1.0006614372099958</v>
       </c>
       <c r="I21" s="21">
-        <v>720.0357916039862</v>
+        <v>726.9104878324572</v>
       </c>
       <c r="J21" s="24">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2412.0898753599427</v>
+        <v>2431.997550380802</v>
       </c>
       <c r="I22" s="22">
-        <v>2412.0898753599427</v>
+        <v>2431.997550380802</v>
       </c>
       <c r="J22" s="25">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.000883780378074</v>
+        <v>1.0006614372099958</v>
       </c>
       <c r="I23">
-        <v>2412.0898753599427</v>
+        <v>2431.997550380802</v>
       </c>
       <c r="J23">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999339</v>
+        <v>0.999242</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>105.64983454063136</v>
+        <v>104.42915730123434</v>
       </c>
       <c r="I14" s="20">
-        <v>105.64983454063136</v>
+        <v>104.42915730123434</v>
       </c>
       <c r="J14" s="23">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0006614372099958</v>
+        <v>1.00075857499985</v>
       </c>
       <c r="I15" s="21">
-        <v>105.64983454063136</v>
+        <v>104.42915730123434</v>
       </c>
       <c r="J15" s="24">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0006614372099958</v>
+        <v>1.00075857499985</v>
       </c>
       <c r="I16" s="21">
-        <v>726.9104878324572</v>
+        <v>729.0926522303906</v>
       </c>
       <c r="J16" s="24">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>726.9104878324572</v>
+        <v>729.0926522303906</v>
       </c>
       <c r="I17" s="21">
-        <v>726.9104878324572</v>
+        <v>729.0926522303906</v>
       </c>
       <c r="J17" s="24">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7023422482260775</v>
+        <v>0.7108968598197435</v>
       </c>
       <c r="I18" s="21">
-        <v>726.9104878324572</v>
+        <v>729.0926522303906</v>
       </c>
       <c r="J18" s="24">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>80.17299434926487</v>
+        <v>78.6596239949882</v>
       </c>
       <c r="I19" s="21">
-        <v>80.17299434926487</v>
+        <v>78.6596239949882</v>
       </c>
       <c r="J19" s="24">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>726.9104878324572</v>
+        <v>729.0926522303906</v>
       </c>
       <c r="I20" s="21">
-        <v>726.9104878324572</v>
+        <v>729.0926522303906</v>
       </c>
       <c r="J20" s="24">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0006614372099958</v>
+        <v>1.00075857499985</v>
       </c>
       <c r="I21" s="21">
-        <v>726.9104878324572</v>
+        <v>729.0926522303906</v>
       </c>
       <c r="J21" s="24">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2431.997550380802</v>
+        <v>2394.194799658141</v>
       </c>
       <c r="I22" s="22">
-        <v>2431.997550380802</v>
+        <v>2394.194799658141</v>
       </c>
       <c r="J22" s="25">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0006614372099958</v>
+        <v>1.00075857499985</v>
       </c>
       <c r="I23">
-        <v>2431.997550380802</v>
+        <v>2394.194799658141</v>
       </c>
       <c r="J23">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999242</v>
+        <v>0.999081</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>104.42915730123434</v>
+        <v>105.76720005685225</v>
       </c>
       <c r="I14" s="20">
-        <v>104.42915730123434</v>
+        <v>105.76720005685225</v>
       </c>
       <c r="J14" s="23">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.00075857499985</v>
+        <v>1.0009198453378656</v>
       </c>
       <c r="I15" s="21">
-        <v>104.42915730123434</v>
+        <v>105.76720005685225</v>
       </c>
       <c r="J15" s="24">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.00075857499985</v>
+        <v>1.0009198453378656</v>
       </c>
       <c r="I16" s="21">
-        <v>729.0926522303906</v>
+        <v>743.7234818798476</v>
       </c>
       <c r="J16" s="24">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>729.0926522303906</v>
+        <v>743.7234818798476</v>
       </c>
       <c r="I17" s="21">
-        <v>729.0926522303906</v>
+        <v>743.7234818798476</v>
       </c>
       <c r="J17" s="24">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7108968598197435</v>
+        <v>0.7209335379213497</v>
       </c>
       <c r="I18" s="21">
-        <v>729.0926522303906</v>
+        <v>743.7234818798476</v>
       </c>
       <c r="J18" s="24">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>78.6596239949882</v>
+        <v>80.73419472495223</v>
       </c>
       <c r="I19" s="21">
-        <v>78.6596239949882</v>
+        <v>80.73419472495223</v>
       </c>
       <c r="J19" s="24">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>729.0926522303906</v>
+        <v>743.7234818798476</v>
       </c>
       <c r="I20" s="21">
-        <v>729.0926522303906</v>
+        <v>743.7234818798476</v>
       </c>
       <c r="J20" s="24">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.00075857499985</v>
+        <v>1.0009198453378656</v>
       </c>
       <c r="I21" s="21">
-        <v>729.0926522303906</v>
+        <v>743.7234818798476</v>
       </c>
       <c r="J21" s="24">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2394.194799658141</v>
+        <v>2439.1916170961113</v>
       </c>
       <c r="I22" s="22">
-        <v>2394.194799658141</v>
+        <v>2439.1916170961113</v>
       </c>
       <c r="J22" s="25">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.00075857499985</v>
+        <v>1.0009198453378656</v>
       </c>
       <c r="I23">
-        <v>2394.194799658141</v>
+        <v>2439.1916170961113</v>
       </c>
       <c r="J23">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999081</v>
+        <v>0.99926</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>105.76720005685225</v>
+        <v>105.00770570221964</v>
       </c>
       <c r="I14" s="20">
-        <v>105.76720005685225</v>
+        <v>105.00770570221964</v>
       </c>
       <c r="J14" s="23">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0009198453378656</v>
+        <v>1.000740548005524</v>
       </c>
       <c r="I15" s="21">
-        <v>105.76720005685225</v>
+        <v>105.00770570221964</v>
       </c>
       <c r="J15" s="24">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0009198453378656</v>
+        <v>1.000740548005524</v>
       </c>
       <c r="I16" s="21">
-        <v>743.7234818798476</v>
+        <v>740.0576426555651</v>
       </c>
       <c r="J16" s="24">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>743.7234818798476</v>
+        <v>740.0576426555651</v>
       </c>
       <c r="I17" s="21">
-        <v>743.7234818798476</v>
+        <v>740.0576426555651</v>
       </c>
       <c r="J17" s="24">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7209335379213497</v>
+        <v>0.7107689690370874</v>
       </c>
       <c r="I18" s="21">
-        <v>743.7234818798476</v>
+        <v>740.0576426555651</v>
       </c>
       <c r="J18" s="24">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>80.73419472495223</v>
+        <v>78.8783699937954</v>
       </c>
       <c r="I19" s="21">
-        <v>80.73419472495223</v>
+        <v>78.8783699937954</v>
       </c>
       <c r="J19" s="24">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>743.7234818798476</v>
+        <v>740.0576426555651</v>
       </c>
       <c r="I20" s="21">
-        <v>743.7234818798476</v>
+        <v>740.0576426555651</v>
       </c>
       <c r="J20" s="24">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0009198453378656</v>
+        <v>1.000740548005524</v>
       </c>
       <c r="I21" s="21">
-        <v>743.7234818798476</v>
+        <v>740.0576426555651</v>
       </c>
       <c r="J21" s="24">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2439.1916170961113</v>
+        <v>2439.945559714188</v>
       </c>
       <c r="I22" s="22">
-        <v>2439.1916170961113</v>
+        <v>2439.945559714188</v>
       </c>
       <c r="J22" s="25">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0009198453378656</v>
+        <v>1.000740548005524</v>
       </c>
       <c r="I23">
-        <v>2439.1916170961113</v>
+        <v>2439.945559714188</v>
       </c>
       <c r="J23">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.99926</v>
+        <v>0.998826</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>105.00770570221964</v>
+        <v>104.47265089214737</v>
       </c>
       <c r="I14" s="20">
-        <v>105.00770570221964</v>
+        <v>104.47265089214737</v>
       </c>
       <c r="J14" s="23">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.000740548005524</v>
+        <v>1.001175379895998</v>
       </c>
       <c r="I15" s="21">
-        <v>105.00770570221964</v>
+        <v>104.47265089214737</v>
       </c>
       <c r="J15" s="24">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.000740548005524</v>
+        <v>1.001175379895998</v>
       </c>
       <c r="I16" s="21">
-        <v>740.0576426555651</v>
+        <v>742.1813208707022</v>
       </c>
       <c r="J16" s="24">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>740.0576426555651</v>
+        <v>742.1813208707022</v>
       </c>
       <c r="I17" s="21">
-        <v>740.0576426555651</v>
+        <v>742.1813208707022</v>
       </c>
       <c r="J17" s="24">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7107689690370874</v>
+        <v>0.7006295390788786</v>
       </c>
       <c r="I18" s="21">
-        <v>740.0576426555651</v>
+        <v>742.1813208707022</v>
       </c>
       <c r="J18" s="24">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>78.8783699937954</v>
+        <v>78.2018089236764</v>
       </c>
       <c r="I19" s="21">
-        <v>78.8783699937954</v>
+        <v>78.2018089236764</v>
       </c>
       <c r="J19" s="24">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>740.0576426555651</v>
+        <v>742.1813208707022</v>
       </c>
       <c r="I20" s="21">
-        <v>740.0576426555651</v>
+        <v>742.1813208707022</v>
       </c>
       <c r="J20" s="24">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.000740548005524</v>
+        <v>1.001175379895998</v>
       </c>
       <c r="I21" s="21">
-        <v>740.0576426555651</v>
+        <v>742.1813208707022</v>
       </c>
       <c r="J21" s="24">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2439.945559714188</v>
+        <v>2404.773203741192</v>
       </c>
       <c r="I22" s="22">
-        <v>2439.945559714188</v>
+        <v>2404.773203741192</v>
       </c>
       <c r="J22" s="25">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.000740548005524</v>
+        <v>1.001175379895998</v>
       </c>
       <c r="I23">
-        <v>2439.945559714188</v>
+        <v>2404.773203741192</v>
       </c>
       <c r="J23">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.998826</v>
+        <v>0.999098</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>104.47265089214737</v>
+        <v>102.26224054096795</v>
       </c>
       <c r="I14" s="20">
-        <v>104.47265089214737</v>
+        <v>102.26224054096795</v>
       </c>
       <c r="J14" s="23">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.001175379895998</v>
+        <v>1.0009028143385332</v>
       </c>
       <c r="I15" s="21">
-        <v>104.47265089214737</v>
+        <v>102.26224054096795</v>
       </c>
       <c r="J15" s="24">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.001175379895998</v>
+        <v>1.0009028143385332</v>
       </c>
       <c r="I16" s="21">
-        <v>742.1813208707022</v>
+        <v>738.1858436309551</v>
       </c>
       <c r="J16" s="24">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>742.1813208707022</v>
+        <v>738.1858436309551</v>
       </c>
       <c r="I17" s="21">
-        <v>742.1813208707022</v>
+        <v>738.1858436309551</v>
       </c>
       <c r="J17" s="24">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7006295390788786</v>
+        <v>0.7005188680189531</v>
       </c>
       <c r="I18" s="21">
-        <v>742.1813208707022</v>
+        <v>738.1858436309551</v>
       </c>
       <c r="J18" s="24">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>78.2018089236764</v>
+        <v>76.94940836634643</v>
       </c>
       <c r="I19" s="21">
-        <v>78.2018089236764</v>
+        <v>76.94940836634643</v>
       </c>
       <c r="J19" s="24">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>742.1813208707022</v>
+        <v>738.1858436309551</v>
       </c>
       <c r="I20" s="21">
-        <v>742.1813208707022</v>
+        <v>738.1858436309551</v>
       </c>
       <c r="J20" s="24">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.001175379895998</v>
+        <v>1.0009028143385332</v>
       </c>
       <c r="I21" s="21">
-        <v>742.1813208707022</v>
+        <v>738.1858436309551</v>
       </c>
       <c r="J21" s="24">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2404.773203741192</v>
+        <v>2376.823895153428</v>
       </c>
       <c r="I22" s="22">
-        <v>2404.773203741192</v>
+        <v>2376.823895153428</v>
       </c>
       <c r="J22" s="25">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.001175379895998</v>
+        <v>1.0009028143385332</v>
       </c>
       <c r="I23">
-        <v>2404.773203741192</v>
+        <v>2376.823895153428</v>
       </c>
       <c r="J23">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999098</v>
+        <v>0.999117</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>102.26224054096795</v>
+        <v>101.91999535589926</v>
       </c>
       <c r="I14" s="20">
-        <v>102.26224054096795</v>
+        <v>101.91999535589926</v>
       </c>
       <c r="J14" s="23">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0009028143385332</v>
+        <v>1.000883780378074</v>
       </c>
       <c r="I15" s="21">
-        <v>102.26224054096795</v>
+        <v>101.91999535589926</v>
       </c>
       <c r="J15" s="24">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0009028143385332</v>
+        <v>1.000883780378074</v>
       </c>
       <c r="I16" s="21">
-        <v>738.1858436309551</v>
+        <v>745.0378684378305</v>
       </c>
       <c r="J16" s="24">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>738.1858436309551</v>
+        <v>745.0378684378305</v>
       </c>
       <c r="I17" s="21">
-        <v>738.1858436309551</v>
+        <v>745.0378684378305</v>
       </c>
       <c r="J17" s="24">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7005188680189531</v>
+        <v>0.7067080231844719</v>
       </c>
       <c r="I18" s="21">
-        <v>738.1858436309551</v>
+        <v>745.0378684378305</v>
       </c>
       <c r="J18" s="24">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>76.94940836634643</v>
+        <v>76.23731755139788</v>
       </c>
       <c r="I19" s="21">
-        <v>76.94940836634643</v>
+        <v>76.23731755139788</v>
       </c>
       <c r="J19" s="24">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>738.1858436309551</v>
+        <v>745.0378684378305</v>
       </c>
       <c r="I20" s="21">
-        <v>738.1858436309551</v>
+        <v>745.0378684378305</v>
       </c>
       <c r="J20" s="24">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0009028143385332</v>
+        <v>1.000883780378074</v>
       </c>
       <c r="I21" s="21">
-        <v>738.1858436309551</v>
+        <v>745.0378684378305</v>
       </c>
       <c r="J21" s="24">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2376.823895153428</v>
+        <v>2351.7566010787523</v>
       </c>
       <c r="I22" s="22">
-        <v>2376.823895153428</v>
+        <v>2351.7566010787523</v>
       </c>
       <c r="J22" s="25">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0009028143385332</v>
+        <v>1.000883780378074</v>
       </c>
       <c r="I23">
-        <v>2376.823895153428</v>
+        <v>2351.7566010787523</v>
       </c>
       <c r="J23">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.999117</v>
+        <v>0.99935</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>101.91999535589926</v>
+        <v>100.83554310301696</v>
       </c>
       <c r="I14" s="20">
-        <v>101.91999535589926</v>
+        <v>100.83554310301696</v>
       </c>
       <c r="J14" s="23">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.000883780378074</v>
+        <v>1.0006504227748036</v>
       </c>
       <c r="I15" s="21">
-        <v>101.91999535589926</v>
+        <v>100.83554310301696</v>
       </c>
       <c r="J15" s="24">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.000883780378074</v>
+        <v>1.0006504227748036</v>
       </c>
       <c r="I16" s="21">
-        <v>745.0378684378305</v>
+        <v>738.6100965627659</v>
       </c>
       <c r="J16" s="24">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>745.0378684378305</v>
+        <v>738.6100965627659</v>
       </c>
       <c r="I17" s="21">
-        <v>745.0378684378305</v>
+        <v>738.6100965627659</v>
       </c>
       <c r="J17" s="24">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7067080231844719</v>
+        <v>0.7056746885475559</v>
       </c>
       <c r="I18" s="21">
-        <v>745.0378684378305</v>
+        <v>738.6100965627659</v>
       </c>
       <c r="J18" s="24">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>76.23731755139788</v>
+        <v>76.44969229999501</v>
       </c>
       <c r="I19" s="21">
-        <v>76.23731755139788</v>
+        <v>76.44969229999501</v>
       </c>
       <c r="J19" s="24">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>745.0378684378305</v>
+        <v>738.6100965627659</v>
       </c>
       <c r="I20" s="21">
-        <v>745.0378684378305</v>
+        <v>738.6100965627659</v>
       </c>
       <c r="J20" s="24">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.000883780378074</v>
+        <v>1.0006504227748036</v>
       </c>
       <c r="I21" s="21">
-        <v>745.0378684378305</v>
+        <v>738.6100965627659</v>
       </c>
       <c r="J21" s="24">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2351.7566010787523</v>
+        <v>2315.08480512333</v>
       </c>
       <c r="I22" s="22">
-        <v>2351.7566010787523</v>
+        <v>2315.08480512333</v>
       </c>
       <c r="J22" s="25">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.000883780378074</v>
+        <v>1.0006504227748036</v>
       </c>
       <c r="I23">
-        <v>2351.7566010787523</v>
+        <v>2315.08480512333</v>
       </c>
       <c r="J23">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.99935</v>
+        <v>0.998675</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>100.83554310301696</v>
+        <v>99.82226450046312</v>
       </c>
       <c r="I14" s="20">
-        <v>100.83554310301696</v>
+        <v>99.82226450046312</v>
       </c>
       <c r="J14" s="23">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0006504227748036</v>
+        <v>1.0013267579542895</v>
       </c>
       <c r="I15" s="21">
-        <v>100.83554310301696</v>
+        <v>99.82226450046312</v>
       </c>
       <c r="J15" s="24">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0006504227748036</v>
+        <v>1.0013267579542895</v>
       </c>
       <c r="I16" s="21">
-        <v>738.6100965627659</v>
+        <v>735.9651538288232</v>
       </c>
       <c r="J16" s="24">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>738.6100965627659</v>
+        <v>735.9651538288232</v>
       </c>
       <c r="I17" s="21">
-        <v>738.6100965627659</v>
+        <v>735.9651538288232</v>
       </c>
       <c r="J17" s="24">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7056746885475559</v>
+        <v>0.705763136155406</v>
       </c>
       <c r="I18" s="21">
-        <v>738.6100965627659</v>
+        <v>735.9651538288232</v>
       </c>
       <c r="J18" s="24">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>76.44969229999501</v>
+        <v>77.51270433324154</v>
       </c>
       <c r="I19" s="21">
-        <v>76.44969229999501</v>
+        <v>77.51270433324154</v>
       </c>
       <c r="J19" s="24">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>738.6100965627659</v>
+        <v>735.9651538288232</v>
       </c>
       <c r="I20" s="21">
-        <v>738.6100965627659</v>
+        <v>735.9651538288232</v>
       </c>
       <c r="J20" s="24">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0006504227748036</v>
+        <v>1.0013267579542895</v>
       </c>
       <c r="I21" s="21">
-        <v>738.6100965627659</v>
+        <v>735.9651538288232</v>
       </c>
       <c r="J21" s="24">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2315.08480512333</v>
+        <v>2308.7791323503643</v>
       </c>
       <c r="I22" s="22">
-        <v>2315.08480512333</v>
+        <v>2308.7791323503643</v>
       </c>
       <c r="J22" s="25">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0006504227748036</v>
+        <v>1.0013267579542895</v>
       </c>
       <c r="I23">
-        <v>2315.08480512333</v>
+        <v>2308.7791323503643</v>
       </c>
       <c r="J23">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.998675</v>
+        <v>0.998741</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>99.82226450046312</v>
+        <v>101.94835297639727</v>
       </c>
       <c r="I14" s="20">
-        <v>99.82226450046312</v>
+        <v>101.94835297639727</v>
       </c>
       <c r="J14" s="23">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0013267579542895</v>
+        <v>1.0012605870791327</v>
       </c>
       <c r="I15" s="21">
-        <v>99.82226450046312</v>
+        <v>101.94835297639727</v>
       </c>
       <c r="J15" s="24">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0013267579542895</v>
+        <v>1.0012605870791327</v>
       </c>
       <c r="I16" s="21">
-        <v>735.9651538288232</v>
+        <v>744.5073347344307</v>
       </c>
       <c r="J16" s="24">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>735.9651538288232</v>
+        <v>744.5073347344307</v>
       </c>
       <c r="I17" s="21">
-        <v>735.9651538288232</v>
+        <v>744.5073347344307</v>
       </c>
       <c r="J17" s="24">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.705763136155406</v>
+        <v>0.7115838841100947</v>
       </c>
       <c r="I18" s="21">
-        <v>735.9651538288232</v>
+        <v>744.5073347344307</v>
       </c>
       <c r="J18" s="24">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>77.51270433324154</v>
+        <v>81.14215797689292</v>
       </c>
       <c r="I19" s="21">
-        <v>77.51270433324154</v>
+        <v>81.14215797689292</v>
       </c>
       <c r="J19" s="24">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>735.9651538288232</v>
+        <v>744.5073347344307</v>
       </c>
       <c r="I20" s="21">
-        <v>735.9651538288232</v>
+        <v>744.5073347344307</v>
       </c>
       <c r="J20" s="24">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0013267579542895</v>
+        <v>1.0012605870791327</v>
       </c>
       <c r="I21" s="21">
-        <v>735.9651538288232</v>
+        <v>744.5073347344307</v>
       </c>
       <c r="J21" s="24">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2308.7791323503643</v>
+        <v>2351.981144260624</v>
       </c>
       <c r="I22" s="22">
-        <v>2308.7791323503643</v>
+        <v>2351.981144260624</v>
       </c>
       <c r="J22" s="25">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0013267579542895</v>
+        <v>1.0012605870791327</v>
       </c>
       <c r="I23">
-        <v>2308.7791323503643</v>
+        <v>2351.981144260624</v>
       </c>
       <c r="J23">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.998741</v>
+        <v>0.998957</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>101.94835297639727</v>
+        <v>99.90420008068415</v>
       </c>
       <c r="I14" s="20">
-        <v>101.94835297639727</v>
+        <v>99.90420008068415</v>
       </c>
       <c r="J14" s="23">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0012605870791327</v>
+        <v>1.0010440889848111</v>
       </c>
       <c r="I15" s="21">
-        <v>101.94835297639727</v>
+        <v>99.90420008068415</v>
       </c>
       <c r="J15" s="24">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0012605870791327</v>
+        <v>1.0010440889848111</v>
       </c>
       <c r="I16" s="21">
-        <v>744.5073347344307</v>
+        <v>751.7140377413642</v>
       </c>
       <c r="J16" s="24">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>744.5073347344307</v>
+        <v>751.7140377413642</v>
       </c>
       <c r="I17" s="21">
-        <v>744.5073347344307</v>
+        <v>751.7140377413642</v>
       </c>
       <c r="J17" s="24">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7115838841100947</v>
+        <v>0.7001172222628201</v>
       </c>
       <c r="I18" s="21">
-        <v>744.5073347344307</v>
+        <v>751.7140377413642</v>
       </c>
       <c r="J18" s="24">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>81.14215797689292</v>
+        <v>78.93232641645236</v>
       </c>
       <c r="I19" s="21">
-        <v>81.14215797689292</v>
+        <v>78.93232641645236</v>
       </c>
       <c r="J19" s="24">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>744.5073347344307</v>
+        <v>751.7140377413642</v>
       </c>
       <c r="I20" s="21">
-        <v>744.5073347344307</v>
+        <v>751.7140377413642</v>
       </c>
       <c r="J20" s="24">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0012605870791327</v>
+        <v>1.0010440889848111</v>
       </c>
       <c r="I21" s="21">
-        <v>744.5073347344307</v>
+        <v>751.7140377413642</v>
       </c>
       <c r="J21" s="24">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2351.981144260624</v>
+        <v>2310.6600183991904</v>
       </c>
       <c r="I22" s="22">
-        <v>2351.981144260624</v>
+        <v>2310.6600183991904</v>
       </c>
       <c r="J22" s="25">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0012605870791327</v>
+        <v>1.0010440889848111</v>
       </c>
       <c r="I23">
-        <v>2351.981144260624</v>
+        <v>2310.6600183991904</v>
       </c>
       <c r="J23">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.998957</v>
+        <v>0.998762</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>99.90420008068415</v>
+        <v>97.97128845510741</v>
       </c>
       <c r="I14" s="20">
-        <v>99.90420008068415</v>
+        <v>97.97128845510741</v>
       </c>
       <c r="J14" s="23">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0010440889848111</v>
+        <v>1.0012395345437652</v>
       </c>
       <c r="I15" s="21">
-        <v>99.90420008068415</v>
+        <v>97.97128845510741</v>
       </c>
       <c r="J15" s="24">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0010440889848111</v>
+        <v>1.0012395345437652</v>
       </c>
       <c r="I16" s="21">
-        <v>751.7140377413642</v>
+        <v>713.8537509436683</v>
       </c>
       <c r="J16" s="24">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>751.7140377413642</v>
+        <v>713.8537509436683</v>
       </c>
       <c r="I17" s="21">
-        <v>751.7140377413642</v>
+        <v>713.8537509436683</v>
       </c>
       <c r="J17" s="24">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.7001172222628201</v>
+        <v>0.6941833990480215</v>
       </c>
       <c r="I18" s="21">
-        <v>751.7140377413642</v>
+        <v>713.8537509436683</v>
       </c>
       <c r="J18" s="24">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>78.93232641645236</v>
+        <v>93.09525192187928</v>
       </c>
       <c r="I19" s="21">
-        <v>78.93232641645236</v>
+        <v>93.09525192187928</v>
       </c>
       <c r="J19" s="24">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>751.7140377413642</v>
+        <v>713.8537509436683</v>
       </c>
       <c r="I20" s="21">
-        <v>751.7140377413642</v>
+        <v>713.8537509436683</v>
       </c>
       <c r="J20" s="24">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0010440889848111</v>
+        <v>1.0012395345437652</v>
       </c>
       <c r="I21" s="21">
-        <v>751.7140377413642</v>
+        <v>713.8537509436683</v>
       </c>
       <c r="J21" s="24">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2310.6600183991904</v>
+        <v>2249.665085375695</v>
       </c>
       <c r="I22" s="22">
-        <v>2310.6600183991904</v>
+        <v>2249.665085375695</v>
       </c>
       <c r="J22" s="25">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0010440889848111</v>
+        <v>1.0012395345437652</v>
       </c>
       <c r="I23">
-        <v>2310.6600183991904</v>
+        <v>2249.665085375695</v>
       </c>
       <c r="J23">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>

--- a/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
+++ b/excel/latest/发射平台模型_全曲线_PonsV2.xlsx
@@ -4548,7 +4548,7 @@
         <v>USDT / USD</v>
       </c>
       <c r="D6" s="5">
-        <v>0.998762</v>
+        <v>0.999185</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -4592,7 +4592,7 @@
         <v>快照时间 / UTC</v>
       </c>
       <c r="D7" s="6">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4972,13 +4972,13 @@
       </c>
       <c r="G14" s="35" t="str"/>
       <c r="H14" s="20">
-        <v>97.97128845510741</v>
+        <v>95.85812437136266</v>
       </c>
       <c r="I14" s="20">
-        <v>97.97128845510741</v>
+        <v>95.85812437136266</v>
       </c>
       <c r="J14" s="23">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="K14" s="35" t="inlineStr">
         <is>
@@ -5088,13 +5088,13 @@
       </c>
       <c r="G15" s="36" t="str"/>
       <c r="H15" s="21">
-        <v>1.0012395345437652</v>
+        <v>1.000815664766785</v>
       </c>
       <c r="I15" s="21">
-        <v>97.97128845510741</v>
+        <v>95.85812437136266</v>
       </c>
       <c r="J15" s="24">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="K15" s="36" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
       </c>
       <c r="G16" s="36" t="str"/>
       <c r="H16" s="21">
-        <v>1.0012395345437652</v>
+        <v>1.000815664766785</v>
       </c>
       <c r="I16" s="21">
-        <v>713.8537509436683</v>
+        <v>701.7319115078789</v>
       </c>
       <c r="J16" s="24">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="K16" s="36" t="inlineStr">
         <is>
@@ -5320,13 +5320,13 @@
       </c>
       <c r="G17" s="36" t="str"/>
       <c r="H17" s="21">
-        <v>713.8537509436683</v>
+        <v>701.7319115078789</v>
       </c>
       <c r="I17" s="21">
-        <v>713.8537509436683</v>
+        <v>701.7319115078789</v>
       </c>
       <c r="J17" s="24">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="K17" s="36" t="inlineStr">
         <is>
@@ -5436,13 +5436,13 @@
       </c>
       <c r="G18" s="36" t="str"/>
       <c r="H18" s="21">
-        <v>0.6941833990480215</v>
+        <v>0.6880037230342729</v>
       </c>
       <c r="I18" s="21">
-        <v>713.8537509436683</v>
+        <v>701.7319115078789</v>
       </c>
       <c r="J18" s="24">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="K18" s="36" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
       </c>
       <c r="G19" s="36" t="str"/>
       <c r="H19" s="21">
-        <v>93.09525192187928</v>
+        <v>88.2219008491921</v>
       </c>
       <c r="I19" s="21">
-        <v>93.09525192187928</v>
+        <v>88.2219008491921</v>
       </c>
       <c r="J19" s="24">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="K19" s="36" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
       </c>
       <c r="G20" s="36" t="str"/>
       <c r="H20" s="21">
-        <v>713.8537509436683</v>
+        <v>701.7319115078789</v>
       </c>
       <c r="I20" s="21">
-        <v>713.8537509436683</v>
+        <v>701.7319115078789</v>
       </c>
       <c r="J20" s="24">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="K20" s="36" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
       </c>
       <c r="G21" s="36" t="str"/>
       <c r="H21" s="21">
-        <v>1.0012395345437652</v>
+        <v>1.000815664766785</v>
       </c>
       <c r="I21" s="21">
-        <v>713.8537509436683</v>
+        <v>701.7319115078789</v>
       </c>
       <c r="J21" s="24">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="K21" s="36" t="inlineStr">
         <is>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="G22" s="37" t="str"/>
       <c r="H22" s="22">
-        <v>2249.665085375695</v>
+        <v>2244.0889324799714</v>
       </c>
       <c r="I22" s="22">
-        <v>2249.665085375695</v>
+        <v>2244.0889324799714</v>
       </c>
       <c r="J22" s="25">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="K22" s="37" t="inlineStr">
         <is>
@@ -6016,13 +6016,13 @@
         <v>0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
       </c>
       <c r="H23">
-        <v>1.0012395345437652</v>
+        <v>1.000815664766785</v>
       </c>
       <c r="I23">
-        <v>2249.665085375695</v>
+        <v>2244.0889324799714</v>
       </c>
       <c r="J23">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
